--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -1131,7 +1131,7 @@
         <v>200</v>
       </c>
       <c r="H18" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I18" s="3">
         <v>600</v>
@@ -2152,7 +2152,7 @@
         <v>100</v>
       </c>
       <c r="F45" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G45" s="3">
         <v>200</v>
@@ -2557,7 +2557,7 @@
         <v>2000</v>
       </c>
       <c r="I54" s="3">
-        <v>1600</v>
+        <v>1700</v>
       </c>
       <c r="J54" s="3">
         <v>1000</v>
@@ -2719,7 +2719,7 @@
         <v>800</v>
       </c>
       <c r="G59" s="3">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="H59" s="3">
         <v>600</v>
@@ -2851,7 +2851,7 @@
         <v>200</v>
       </c>
       <c r="G62" s="3">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -3441,7 +3441,7 @@
         <v>2200</v>
       </c>
       <c r="G76" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="H76" s="3">
         <v>1300</v>

--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
   <si>
     <t>JZXN</t>
   </si>
@@ -656,69 +656,70 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E7" s="2">
         <v>45046</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44865</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44681</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44500</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44316</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44135</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43951</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43769</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43585</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N7" s="2" t="s">
         <v>3</v>
       </c>
@@ -728,41 +729,44 @@
       <c r="P7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>100</v>
+        <v>5900</v>
       </c>
       <c r="E8" s="3">
         <v>900</v>
       </c>
       <c r="F8" s="3">
+        <v>5900</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4100</v>
+      </c>
+      <c r="H8" s="3">
+        <v>9300</v>
+      </c>
+      <c r="I8" s="3">
+        <v>4600</v>
+      </c>
+      <c r="J8" s="3">
+        <v>8200</v>
+      </c>
+      <c r="K8" s="3">
+        <v>200</v>
+      </c>
+      <c r="L8" s="3">
+        <v>1100</v>
+      </c>
+      <c r="M8" s="3">
         <v>600</v>
       </c>
-      <c r="G8" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>600</v>
-      </c>
-      <c r="I8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J8" s="3">
-        <v>200</v>
-      </c>
-      <c r="K8" s="3">
-        <v>1100</v>
-      </c>
-      <c r="L8" s="3">
-        <v>600</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N8" s="3" t="s">
         <v>3</v>
       </c>
@@ -772,41 +776,44 @@
       <c r="P8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>100</v>
+        <v>4600</v>
       </c>
       <c r="E9" s="3">
         <v>900</v>
       </c>
       <c r="F9" s="3">
-        <v>500</v>
+        <v>6300</v>
       </c>
       <c r="G9" s="3">
-        <v>700</v>
+        <v>3600</v>
       </c>
       <c r="H9" s="3">
+        <v>4900</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J9" s="3">
+        <v>2200</v>
+      </c>
+      <c r="K9" s="3">
+        <v>100</v>
+      </c>
+      <c r="L9" s="3">
+        <v>400</v>
+      </c>
+      <c r="M9" s="3">
         <v>200</v>
       </c>
-      <c r="I9" s="3">
-        <v>300</v>
-      </c>
-      <c r="J9" s="3">
-        <v>100</v>
-      </c>
-      <c r="K9" s="3">
-        <v>400</v>
-      </c>
-      <c r="L9" s="3">
-        <v>200</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>3</v>
       </c>
@@ -816,41 +823,44 @@
       <c r="P9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>1300</v>
       </c>
       <c r="E10" s="3">
         <v>0</v>
       </c>
       <c r="F10" s="3">
+        <v>-400</v>
+      </c>
+      <c r="G10" s="3">
+        <v>500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4400</v>
+      </c>
+      <c r="I10" s="3">
+        <v>3100</v>
+      </c>
+      <c r="J10" s="3">
+        <v>6000</v>
+      </c>
+      <c r="K10" s="3">
         <v>100</v>
       </c>
-      <c r="G10" s="3">
-        <v>600</v>
-      </c>
-      <c r="H10" s="3">
-        <v>400</v>
-      </c>
-      <c r="I10" s="3">
-        <v>800</v>
-      </c>
-      <c r="J10" s="3">
-        <v>100</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>300</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>3</v>
       </c>
@@ -860,8 +870,11 @@
       <c r="P10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -878,8 +891,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -922,8 +936,11 @@
       <c r="P12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -966,8 +983,11 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1010,8 +1030,11 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1054,8 +1077,11 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1069,41 +1095,42 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1000</v>
+        <v>15400</v>
       </c>
       <c r="E17" s="3">
-        <v>3200</v>
+        <v>7300</v>
       </c>
       <c r="F17" s="3">
-        <v>1400</v>
+        <v>22600</v>
       </c>
       <c r="G17" s="3">
-        <v>1100</v>
+        <v>10200</v>
       </c>
       <c r="H17" s="3">
-        <v>400</v>
+        <v>8200</v>
       </c>
       <c r="I17" s="3">
-        <v>500</v>
+        <v>2800</v>
       </c>
       <c r="J17" s="3">
+        <v>3800</v>
+      </c>
+      <c r="K17" s="3">
         <v>200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>300</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1113,41 +1140,44 @@
       <c r="P17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-900</v>
+        <v>-9500</v>
       </c>
       <c r="E18" s="3">
-        <v>-2400</v>
+        <v>-6400</v>
       </c>
       <c r="F18" s="3">
-        <v>-800</v>
+        <v>-16700</v>
       </c>
       <c r="G18" s="3">
-        <v>200</v>
+        <v>-6100</v>
       </c>
       <c r="H18" s="3">
+        <v>1100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>0</v>
+      </c>
+      <c r="L18" s="3">
+        <v>500</v>
+      </c>
+      <c r="M18" s="3">
         <v>300</v>
       </c>
-      <c r="I18" s="3">
-        <v>600</v>
-      </c>
-      <c r="J18" s="3">
-        <v>0</v>
-      </c>
-      <c r="K18" s="3">
-        <v>500</v>
-      </c>
-      <c r="L18" s="3">
-        <v>300</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1157,8 +1187,11 @@
       <c r="P18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1175,22 +1208,23 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20" s="3">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="3">
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="G20" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1207,8 +1241,8 @@
       <c r="L20" s="3">
         <v>0</v>
       </c>
-      <c r="M20" s="3" t="s">
-        <v>3</v>
+      <c r="M20" s="3">
+        <v>0</v>
       </c>
       <c r="N20" s="3" t="s">
         <v>3</v>
@@ -1219,41 +1253,44 @@
       <c r="P20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-900</v>
+        <v>-9400</v>
       </c>
       <c r="E21" s="3">
-        <v>-2100</v>
+        <v>-6200</v>
       </c>
       <c r="F21" s="3">
-        <v>-600</v>
+        <v>-14800</v>
       </c>
       <c r="G21" s="3">
-        <v>200</v>
+        <v>-4600</v>
       </c>
       <c r="H21" s="3">
-        <v>200</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+        <v>1200</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1800</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
         <v>500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>300</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1263,22 +1300,25 @@
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="E22" s="3">
         <v>200</v>
       </c>
       <c r="F22" s="3">
-        <v>100</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+        <v>1300</v>
+      </c>
+      <c r="G22" s="3">
+        <v>500</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1295,8 +1335,8 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
+      <c r="M22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N22" s="3">
         <v>0</v>
@@ -1307,41 +1347,44 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-900</v>
+        <v>-9800</v>
       </c>
       <c r="E23" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F23" s="3">
-        <v>-700</v>
+        <v>-16400</v>
       </c>
       <c r="G23" s="3">
-        <v>200</v>
+        <v>-5100</v>
       </c>
       <c r="H23" s="3">
-        <v>200</v>
+        <v>1100</v>
       </c>
       <c r="I23" s="3">
-        <v>600</v>
+        <v>1800</v>
       </c>
       <c r="J23" s="3">
-        <v>0</v>
+        <v>4400</v>
       </c>
       <c r="K23" s="3">
+        <v>0</v>
+      </c>
+      <c r="L23" s="3">
         <v>500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>300</v>
       </c>
-      <c r="M23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1351,13 +1394,16 @@
       <c r="P23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24" s="3">
         <v>0</v>
@@ -1369,22 +1415,22 @@
         <v>100</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="I24" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J24" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>100</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1395,8 +1441,11 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1439,41 +1488,44 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-900</v>
+        <v>-9900</v>
       </c>
       <c r="E26" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F26" s="3">
-        <v>-700</v>
+        <v>-16400</v>
       </c>
       <c r="G26" s="3">
-        <v>100</v>
+        <v>-5300</v>
       </c>
       <c r="H26" s="3">
+        <v>600</v>
+      </c>
+      <c r="I26" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J26" s="3">
+        <v>3400</v>
+      </c>
+      <c r="K26" s="3">
+        <v>0</v>
+      </c>
+      <c r="L26" s="3">
+        <v>400</v>
+      </c>
+      <c r="M26" s="3">
         <v>200</v>
       </c>
-      <c r="I26" s="3">
-        <v>500</v>
-      </c>
-      <c r="J26" s="3">
-        <v>0</v>
-      </c>
-      <c r="K26" s="3">
-        <v>400</v>
-      </c>
-      <c r="L26" s="3">
-        <v>200</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1483,41 +1535,44 @@
       <c r="P26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-900</v>
+        <v>-9900</v>
       </c>
       <c r="E27" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F27" s="3">
-        <v>-700</v>
+        <v>-16300</v>
       </c>
       <c r="G27" s="3">
-        <v>100</v>
+        <v>-5200</v>
       </c>
       <c r="H27" s="3">
+        <v>600</v>
+      </c>
+      <c r="I27" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J27" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K27" s="3">
+        <v>0</v>
+      </c>
+      <c r="L27" s="3">
+        <v>400</v>
+      </c>
+      <c r="M27" s="3">
         <v>200</v>
       </c>
-      <c r="I27" s="3">
-        <v>500</v>
-      </c>
-      <c r="J27" s="3">
-        <v>0</v>
-      </c>
-      <c r="K27" s="3">
-        <v>400</v>
-      </c>
-      <c r="L27" s="3">
-        <v>200</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1527,8 +1582,11 @@
       <c r="P27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1571,31 +1629,34 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
+        <v>500</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
+        <v>-500</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -1615,8 +1676,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1659,8 +1723,11 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1703,22 +1770,25 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E32" s="3">
-        <v>-200</v>
+        <v>-100</v>
       </c>
       <c r="F32" s="3">
-        <v>-200</v>
+        <v>-1700</v>
       </c>
       <c r="G32" s="3">
-        <v>0</v>
+        <v>-1400</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1735,8 +1805,8 @@
       <c r="L32" s="3">
         <v>0</v>
       </c>
-      <c r="M32" s="3" t="s">
-        <v>3</v>
+      <c r="M32" s="3">
+        <v>0</v>
       </c>
       <c r="N32" s="3" t="s">
         <v>3</v>
@@ -1747,41 +1817,44 @@
       <c r="P32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-900</v>
+        <v>-9400</v>
       </c>
       <c r="E33" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F33" s="3">
-        <v>-700</v>
+        <v>-16800</v>
       </c>
       <c r="G33" s="3">
-        <v>100</v>
+        <v>-5200</v>
       </c>
       <c r="H33" s="3">
+        <v>800</v>
+      </c>
+      <c r="I33" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J33" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K33" s="3">
+        <v>0</v>
+      </c>
+      <c r="L33" s="3">
+        <v>400</v>
+      </c>
+      <c r="M33" s="3">
         <v>200</v>
       </c>
-      <c r="I33" s="3">
-        <v>500</v>
-      </c>
-      <c r="J33" s="3">
-        <v>0</v>
-      </c>
-      <c r="K33" s="3">
-        <v>400</v>
-      </c>
-      <c r="L33" s="3">
-        <v>200</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1791,8 +1864,11 @@
       <c r="P33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1835,41 +1911,44 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-900</v>
+        <v>-9400</v>
       </c>
       <c r="E35" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F35" s="3">
-        <v>-700</v>
+        <v>-16800</v>
       </c>
       <c r="G35" s="3">
-        <v>100</v>
+        <v>-5200</v>
       </c>
       <c r="H35" s="3">
+        <v>800</v>
+      </c>
+      <c r="I35" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J35" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K35" s="3">
+        <v>0</v>
+      </c>
+      <c r="L35" s="3">
+        <v>400</v>
+      </c>
+      <c r="M35" s="3">
         <v>200</v>
       </c>
-      <c r="I35" s="3">
-        <v>500</v>
-      </c>
-      <c r="J35" s="3">
-        <v>0</v>
-      </c>
-      <c r="K35" s="3">
-        <v>400</v>
-      </c>
-      <c r="L35" s="3">
-        <v>200</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1879,46 +1958,49 @@
       <c r="P35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E38" s="2">
         <v>45046</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44865</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44681</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44500</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44316</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44135</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43951</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43769</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43585</v>
       </c>
-      <c r="M38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1928,8 +2010,11 @@
       <c r="P38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1946,8 +2031,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1964,34 +2050,35 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>100</v>
+        <v>1200</v>
       </c>
       <c r="E41" s="3">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F41" s="3">
+        <v>2300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>6000</v>
+      </c>
+      <c r="H41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="I41" s="3">
+        <v>700</v>
+      </c>
+      <c r="J41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>100</v>
-      </c>
-      <c r="I41" s="3">
-        <v>100</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>3</v>
+      <c r="K41" s="3">
+        <v>0</v>
       </c>
       <c r="L41" s="3" t="s">
         <v>3</v>
@@ -2008,8 +2095,11 @@
       <c r="P41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2017,16 +2107,16 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="G42" s="3">
-        <v>200</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
+        <v>2100</v>
+      </c>
+      <c r="H42" s="3">
+        <v>1200</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>3</v>
@@ -2043,8 +2133,8 @@
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
+      <c r="N42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O42" s="3">
         <v>0</v>
@@ -2052,35 +2142,38 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>1000</v>
+        <v>7500</v>
       </c>
       <c r="E43" s="3">
-        <v>1100</v>
+        <v>7000</v>
       </c>
       <c r="F43" s="3">
-        <v>1500</v>
+        <v>14600</v>
       </c>
       <c r="G43" s="3">
-        <v>1600</v>
+        <v>10900</v>
       </c>
       <c r="H43" s="3">
-        <v>800</v>
+        <v>11800</v>
       </c>
       <c r="I43" s="3">
-        <v>700</v>
+        <v>5500</v>
       </c>
       <c r="J43" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K43" s="3">
         <v>600</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2096,34 +2189,37 @@
       <c r="P43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>600</v>
+      </c>
+      <c r="G44" s="3">
+        <v>400</v>
+      </c>
+      <c r="H44" s="3">
+        <v>300</v>
+      </c>
+      <c r="I44" s="3">
         <v>100</v>
       </c>
-      <c r="E44" s="3">
-        <v>100</v>
-      </c>
-      <c r="F44" s="3">
-        <v>100</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
       <c r="J44" s="3">
-        <v>0</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>3</v>
+        <v>200</v>
+      </c>
+      <c r="K44" s="3">
+        <v>0</v>
       </c>
       <c r="L44" s="3" t="s">
         <v>3</v>
@@ -2140,35 +2236,38 @@
       <c r="P44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E45" s="3">
+        <v>300</v>
+      </c>
+      <c r="F45" s="3">
+        <v>700</v>
+      </c>
+      <c r="G45" s="3">
+        <v>4000</v>
+      </c>
+      <c r="H45" s="3">
+        <v>1600</v>
+      </c>
+      <c r="I45" s="3">
+        <v>200</v>
+      </c>
+      <c r="J45" s="3">
+        <v>600</v>
+      </c>
+      <c r="K45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
-        <v>600</v>
-      </c>
-      <c r="G45" s="3">
-        <v>200</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>100</v>
-      </c>
-      <c r="J45" s="3">
-        <v>100</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2184,35 +2283,38 @@
       <c r="P45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>1200</v>
+        <v>10500</v>
       </c>
       <c r="E46" s="3">
-        <v>1700</v>
+        <v>8700</v>
       </c>
       <c r="F46" s="3">
-        <v>3200</v>
+        <v>12200</v>
       </c>
       <c r="G46" s="3">
-        <v>3100</v>
+        <v>23300</v>
       </c>
       <c r="H46" s="3">
-        <v>900</v>
+        <v>22200</v>
       </c>
       <c r="I46" s="3">
-        <v>900</v>
+        <v>6500</v>
       </c>
       <c r="J46" s="3">
+        <v>6500</v>
+      </c>
+      <c r="K46" s="3">
         <v>700</v>
       </c>
-      <c r="K46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2228,35 +2330,38 @@
       <c r="P46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E47" s="3">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="F47" s="3">
-        <v>400</v>
+        <v>1600</v>
       </c>
       <c r="G47" s="3">
-        <v>600</v>
+        <v>2700</v>
       </c>
       <c r="H47" s="3">
-        <v>1100</v>
+        <v>4100</v>
       </c>
       <c r="I47" s="3">
-        <v>700</v>
+        <v>7900</v>
       </c>
       <c r="J47" s="3">
+        <v>5300</v>
+      </c>
+      <c r="K47" s="3">
         <v>300</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2272,34 +2377,37 @@
       <c r="P47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>200</v>
+        <v>900</v>
       </c>
       <c r="E48" s="3">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="F48" s="3">
+        <v>1400</v>
+      </c>
+      <c r="G48" s="3">
+        <v>1100</v>
+      </c>
+      <c r="H48" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I48" s="3">
         <v>100</v>
       </c>
-      <c r="G48" s="3">
-        <v>200</v>
-      </c>
-      <c r="H48" s="3">
-        <v>0</v>
-      </c>
-      <c r="I48" s="3">
-        <v>0</v>
-      </c>
       <c r="J48" s="3">
-        <v>0</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="K48" s="3">
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>3</v>
@@ -2316,8 +2424,11 @@
       <c r="P48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2342,8 +2453,8 @@
       <c r="J49" s="3">
         <v>0</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>3</v>
+      <c r="K49" s="3">
+        <v>0</v>
       </c>
       <c r="L49" s="3" t="s">
         <v>3</v>
@@ -2360,8 +2471,11 @@
       <c r="P49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2404,8 +2518,11 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2448,8 +2565,11 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2463,10 +2583,10 @@
         <v>100</v>
       </c>
       <c r="G52" s="3">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I52" s="3">
         <v>0</v>
@@ -2474,8 +2594,8 @@
       <c r="J52" s="3">
         <v>0</v>
       </c>
-      <c r="K52" s="3" t="s">
-        <v>3</v>
+      <c r="K52" s="3">
+        <v>0</v>
       </c>
       <c r="L52" s="3" t="s">
         <v>3</v>
@@ -2492,8 +2612,11 @@
       <c r="P52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2536,35 +2659,38 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>1400</v>
+        <v>11400</v>
       </c>
       <c r="E54" s="3">
-        <v>2100</v>
+        <v>10400</v>
       </c>
       <c r="F54" s="3">
-        <v>3800</v>
+        <v>15300</v>
       </c>
       <c r="G54" s="3">
-        <v>3900</v>
+        <v>27500</v>
       </c>
       <c r="H54" s="3">
-        <v>2000</v>
+        <v>28200</v>
       </c>
       <c r="I54" s="3">
-        <v>1700</v>
+        <v>14500</v>
       </c>
       <c r="J54" s="3">
+        <v>11900</v>
+      </c>
+      <c r="K54" s="3">
         <v>1000</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2580,8 +2706,11 @@
       <c r="P54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2598,8 +2727,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2616,8 +2746,9 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2634,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="K57" s="3">
+        <v>0</v>
       </c>
       <c r="L57" s="3" t="s">
         <v>3</v>
@@ -2660,22 +2791,25 @@
       <c r="P57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
         <v>400</v>
       </c>
       <c r="F58" s="3">
-        <v>600</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>2800</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4200</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2692,8 +2826,8 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
@@ -2704,35 +2838,38 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>800</v>
+        <v>6700</v>
       </c>
       <c r="E59" s="3">
-        <v>800</v>
+        <v>5600</v>
       </c>
       <c r="F59" s="3">
-        <v>800</v>
+        <v>5500</v>
       </c>
       <c r="G59" s="3">
-        <v>600</v>
+        <v>5400</v>
       </c>
       <c r="H59" s="3">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="I59" s="3">
-        <v>500</v>
+        <v>4600</v>
       </c>
       <c r="J59" s="3">
+        <v>3600</v>
+      </c>
+      <c r="K59" s="3">
         <v>300</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2748,35 +2885,38 @@
       <c r="P59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>800</v>
+        <v>6700</v>
       </c>
       <c r="E60" s="3">
-        <v>1200</v>
+        <v>6100</v>
       </c>
       <c r="F60" s="3">
-        <v>1300</v>
+        <v>8300</v>
       </c>
       <c r="G60" s="3">
-        <v>600</v>
+        <v>9700</v>
       </c>
       <c r="H60" s="3">
-        <v>600</v>
+        <v>4000</v>
       </c>
       <c r="I60" s="3">
-        <v>500</v>
+        <v>4600</v>
       </c>
       <c r="J60" s="3">
+        <v>3700</v>
+      </c>
+      <c r="K60" s="3">
         <v>300</v>
       </c>
-      <c r="K60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2792,8 +2932,11 @@
       <c r="P60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2836,25 +2979,28 @@
       <c r="P61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E62" s="3">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="F62" s="3">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="G62" s="3">
-        <v>300</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
+        <v>1600</v>
+      </c>
+      <c r="H62" s="3">
+        <v>1800</v>
       </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
@@ -2871,8 +3017,8 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3">
-        <v>0</v>
+      <c r="N62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O62" s="3">
         <v>0</v>
@@ -2880,8 +3026,11 @@
       <c r="P62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2924,8 +3073,11 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2968,8 +3120,11 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3012,35 +3167,38 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="E66" s="3">
-        <v>1300</v>
+        <v>6900</v>
       </c>
       <c r="F66" s="3">
-        <v>1600</v>
+        <v>9400</v>
       </c>
       <c r="G66" s="3">
-        <v>800</v>
+        <v>11500</v>
       </c>
       <c r="H66" s="3">
-        <v>700</v>
+        <v>6100</v>
       </c>
       <c r="I66" s="3">
-        <v>600</v>
+        <v>5000</v>
       </c>
       <c r="J66" s="3">
+        <v>4100</v>
+      </c>
+      <c r="K66" s="3">
         <v>400</v>
       </c>
-      <c r="K66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3056,8 +3214,11 @@
       <c r="P66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3074,8 +3235,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3118,8 +3280,11 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3162,8 +3327,11 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3206,8 +3374,11 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3250,35 +3421,38 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-2100</v>
+        <v>-17800</v>
       </c>
       <c r="E72" s="3">
-        <v>-1200</v>
+        <v>-15000</v>
       </c>
       <c r="F72" s="3">
-        <v>400</v>
+        <v>-8500</v>
       </c>
       <c r="G72" s="3">
-        <v>1200</v>
+        <v>3100</v>
       </c>
       <c r="H72" s="3">
-        <v>1200</v>
+        <v>8400</v>
       </c>
       <c r="I72" s="3">
-        <v>1000</v>
+        <v>8900</v>
       </c>
       <c r="J72" s="3">
+        <v>7500</v>
+      </c>
+      <c r="K72" s="3">
         <v>600</v>
       </c>
-      <c r="K72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3294,8 +3468,11 @@
       <c r="P72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3338,8 +3515,11 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3382,8 +3562,11 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3426,35 +3609,38 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>500</v>
+        <v>4200</v>
       </c>
       <c r="E76" s="3">
-        <v>800</v>
+        <v>3500</v>
       </c>
       <c r="F76" s="3">
-        <v>2200</v>
+        <v>5900</v>
       </c>
       <c r="G76" s="3">
-        <v>3100</v>
+        <v>16100</v>
       </c>
       <c r="H76" s="3">
-        <v>1300</v>
+        <v>22100</v>
       </c>
       <c r="I76" s="3">
-        <v>1100</v>
+        <v>9500</v>
       </c>
       <c r="J76" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K76" s="3">
         <v>600</v>
       </c>
-      <c r="K76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3470,8 +3656,11 @@
       <c r="P76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3514,46 +3703,49 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45230</v>
+      </c>
+      <c r="E80" s="2">
         <v>45046</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44865</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44681</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44500</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44316</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44135</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43951</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43769</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43585</v>
       </c>
-      <c r="M80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="N80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3563,41 +3755,44 @@
       <c r="P80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-900</v>
+        <v>-9400</v>
       </c>
       <c r="E81" s="3">
-        <v>-2300</v>
+        <v>-6500</v>
       </c>
       <c r="F81" s="3">
-        <v>-700</v>
+        <v>-16800</v>
       </c>
       <c r="G81" s="3">
-        <v>100</v>
+        <v>-5200</v>
       </c>
       <c r="H81" s="3">
+        <v>800</v>
+      </c>
+      <c r="I81" s="3">
+        <v>1300</v>
+      </c>
+      <c r="J81" s="3">
+        <v>3500</v>
+      </c>
+      <c r="K81" s="3">
+        <v>0</v>
+      </c>
+      <c r="L81" s="3">
+        <v>400</v>
+      </c>
+      <c r="M81" s="3">
         <v>200</v>
       </c>
-      <c r="I81" s="3">
-        <v>500</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0</v>
-      </c>
-      <c r="K81" s="3">
-        <v>400</v>
-      </c>
-      <c r="L81" s="3">
-        <v>200</v>
-      </c>
-      <c r="M81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3802,11 @@
       <c r="P81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3625,37 +3823,38 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E83" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
         <v>0</v>
       </c>
       <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>0</v>
       </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
       </c>
       <c r="M83" s="3" t="s">
         <v>3</v>
@@ -3669,8 +3868,11 @@
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3713,8 +3915,11 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3757,8 +3962,11 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3801,8 +4009,11 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3845,8 +4056,11 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3889,38 +4103,41 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-400</v>
+        <v>-5500</v>
       </c>
       <c r="E89" s="3">
-        <v>-1200</v>
+        <v>-2700</v>
       </c>
       <c r="F89" s="3">
-        <v>-600</v>
+        <v>-8900</v>
       </c>
       <c r="G89" s="3">
-        <v>-700</v>
+        <v>-4300</v>
       </c>
       <c r="H89" s="3">
-        <v>0</v>
-      </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
+        <v>-4800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-100</v>
       </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K89" s="3">
+      <c r="K89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L89" s="3">
         <v>-100</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3933,8 +4150,11 @@
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3951,8 +4171,9 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3980,8 +4201,8 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3" t="s">
         <v>3</v>
@@ -3995,8 +4216,11 @@
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4039,8 +4263,11 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4083,37 +4310,40 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>100</v>
+        <v>1300</v>
       </c>
       <c r="E94" s="3">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F94" s="3">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="G94" s="3">
-        <v>-200</v>
+        <v>-900</v>
       </c>
       <c r="H94" s="3">
-        <v>0</v>
-      </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
+        <v>-1500</v>
+      </c>
+      <c r="I94" s="3">
+        <v>0</v>
       </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K94" s="3">
-        <v>0</v>
-      </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
+      <c r="K94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L94" s="3">
+        <v>0</v>
       </c>
       <c r="M94" s="3" t="s">
         <v>3</v>
@@ -4127,8 +4357,11 @@
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4145,8 +4378,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4189,8 +4423,11 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4233,8 +4470,11 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4277,8 +4517,11 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4321,38 +4564,41 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="E100" s="3">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="F100" s="3">
-        <v>600</v>
+        <v>3600</v>
       </c>
       <c r="G100" s="3">
-        <v>1800</v>
+        <v>4200</v>
       </c>
       <c r="H100" s="3">
-        <v>0</v>
-      </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
+        <v>12800</v>
+      </c>
+      <c r="I100" s="3">
+        <v>0</v>
       </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K100" s="3">
+      <c r="K100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="3">
         <v>100</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4365,37 +4611,40 @@
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-200</v>
       </c>
       <c r="E101" s="3">
         <v>0</v>
       </c>
       <c r="F101" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="G101" s="3">
-        <v>0</v>
+        <v>-400</v>
       </c>
       <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="I101" s="3">
+        <v>100</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -4409,38 +4658,41 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-200</v>
+        <v>-1200</v>
       </c>
       <c r="E102" s="3">
-        <v>-700</v>
+        <v>-1500</v>
       </c>
       <c r="F102" s="3">
-        <v>-200</v>
+        <v>-5000</v>
       </c>
       <c r="G102" s="3">
-        <v>900</v>
+        <v>-1400</v>
       </c>
       <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
+        <v>6600</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-100</v>
       </c>
       <c r="J102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K102" s="3">
+      <c r="K102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="3">
         <v>-100</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4451,6 +4703,9 @@
         <v>3</v>
       </c>
       <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
   <si>
     <t>JZXN</t>
   </si>
@@ -656,73 +656,74 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E7" s="2">
         <v>45230</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45046</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44865</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44681</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44500</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44316</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44135</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43951</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43769</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43585</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O7" s="2" t="s">
         <v>3</v>
       </c>
@@ -732,44 +733,47 @@
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E8" s="3">
         <v>5900</v>
       </c>
-      <c r="E8" s="3">
-        <v>900</v>
-      </c>
       <c r="F8" s="3">
+        <v>600</v>
+      </c>
+      <c r="G8" s="3">
         <v>5900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>9300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>600</v>
       </c>
-      <c r="N8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O8" s="3" t="s">
         <v>3</v>
       </c>
@@ -779,44 +783,47 @@
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E9" s="3">
         <v>4600</v>
       </c>
-      <c r="E9" s="3">
-        <v>900</v>
-      </c>
       <c r="F9" s="3">
+        <v>800</v>
+      </c>
+      <c r="G9" s="3">
         <v>6300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>200</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>3</v>
       </c>
@@ -826,44 +833,47 @@
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
       <c r="F10" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G10" s="3">
         <v>-400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>300</v>
       </c>
-      <c r="N10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O10" s="3" t="s">
         <v>3</v>
       </c>
@@ -873,8 +883,11 @@
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -892,8 +905,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -939,8 +953,11 @@
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -986,8 +1003,11 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1033,8 +1053,11 @@
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1080,8 +1103,11 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,44 +1122,45 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>18100</v>
+      </c>
+      <c r="E17" s="3">
         <v>15400</v>
       </c>
-      <c r="E17" s="3">
-        <v>7300</v>
-      </c>
       <c r="F17" s="3">
+        <v>6700</v>
+      </c>
+      <c r="G17" s="3">
         <v>22600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>8200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>300</v>
       </c>
-      <c r="N17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,44 +1170,47 @@
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E18" s="3">
         <v>-9500</v>
       </c>
-      <c r="E18" s="3">
-        <v>-6400</v>
-      </c>
       <c r="F18" s="3">
+        <v>-6100</v>
+      </c>
+      <c r="G18" s="3">
         <v>-16700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-6100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>4400</v>
       </c>
-      <c r="K18" s="3">
-        <v>0</v>
-      </c>
       <c r="L18" s="3">
+        <v>0</v>
+      </c>
+      <c r="M18" s="3">
         <v>500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>300</v>
       </c>
-      <c r="N18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1190,8 +1220,11 @@
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1209,26 +1242,27 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>100</v>
       </c>
       <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
         <v>1700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1400</v>
       </c>
-      <c r="H20" s="3">
-        <v>0</v>
-      </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
@@ -1244,8 +1278,8 @@
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>3</v>
+      <c r="N20" s="3">
+        <v>0</v>
       </c>
       <c r="O20" s="3" t="s">
         <v>3</v>
@@ -1256,44 +1290,47 @@
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E21" s="3">
         <v>-9400</v>
       </c>
-      <c r="E21" s="3">
-        <v>-6200</v>
-      </c>
       <c r="F21" s="3">
+        <v>-6000</v>
+      </c>
+      <c r="G21" s="3">
         <v>-14800</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-4600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1800</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
         <v>500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>300</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1303,26 +1340,29 @@
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>100</v>
+      </c>
+      <c r="E22" s="3">
         <v>300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>500</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1338,8 +1378,8 @@
       <c r="M22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
+      <c r="N22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O22" s="3">
         <v>0</v>
@@ -1350,44 +1390,47 @@
       <c r="Q22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-9800</v>
       </c>
-      <c r="E23" s="3">
-        <v>-6500</v>
-      </c>
       <c r="F23" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G23" s="3">
         <v>-16400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-5100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4400</v>
       </c>
-      <c r="K23" s="3">
-        <v>0</v>
-      </c>
       <c r="L23" s="3">
+        <v>0</v>
+      </c>
+      <c r="M23" s="3">
         <v>500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>300</v>
       </c>
-      <c r="N23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1397,43 +1440,46 @@
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
         <v>100</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
       <c r="F24" s="3">
         <v>0</v>
       </c>
       <c r="G24" s="3">
+        <v>0</v>
+      </c>
+      <c r="H24" s="3">
         <v>100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1000</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>100</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1444,8 +1490,11 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1491,44 +1540,47 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-9900</v>
       </c>
-      <c r="E26" s="3">
-        <v>-6500</v>
-      </c>
       <c r="F26" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G26" s="3">
         <v>-16400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-5300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3400</v>
       </c>
-      <c r="K26" s="3">
-        <v>0</v>
-      </c>
       <c r="L26" s="3">
+        <v>0</v>
+      </c>
+      <c r="M26" s="3">
         <v>400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200</v>
       </c>
-      <c r="N26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1538,44 +1590,47 @@
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-15900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-9900</v>
       </c>
-      <c r="E27" s="3">
-        <v>-6500</v>
-      </c>
       <c r="F27" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-16300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-5200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3500</v>
       </c>
-      <c r="K27" s="3">
-        <v>0</v>
-      </c>
       <c r="L27" s="3">
+        <v>0</v>
+      </c>
+      <c r="M27" s="3">
         <v>400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>200</v>
       </c>
-      <c r="N27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1585,8 +1640,11 @@
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1632,34 +1690,37 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>100</v>
+      </c>
+      <c r="E29" s="3">
         <v>500</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="F29" s="3">
+        <v>-200</v>
+      </c>
+      <c r="G29" s="3">
         <v>-500</v>
       </c>
-      <c r="G29" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H29" s="3">
+      <c r="H29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="3">
         <v>200</v>
       </c>
-      <c r="I29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -1679,8 +1740,11 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1726,8 +1790,11 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1773,26 +1840,29 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>-100</v>
       </c>
       <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
         <v>-1700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1400</v>
       </c>
-      <c r="H32" s="3">
-        <v>0</v>
-      </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
@@ -1808,8 +1878,8 @@
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3" t="s">
-        <v>3</v>
+      <c r="N32" s="3">
+        <v>0</v>
       </c>
       <c r="O32" s="3" t="s">
         <v>3</v>
@@ -1820,44 +1890,47 @@
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-9400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-6500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-16800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-5200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3500</v>
       </c>
-      <c r="K33" s="3">
-        <v>0</v>
-      </c>
       <c r="L33" s="3">
+        <v>0</v>
+      </c>
+      <c r="M33" s="3">
         <v>400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>200</v>
       </c>
-      <c r="N33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1867,8 +1940,11 @@
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1914,44 +1990,47 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-9400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-6500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-16800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-5200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3500</v>
       </c>
-      <c r="K35" s="3">
-        <v>0</v>
-      </c>
       <c r="L35" s="3">
+        <v>0</v>
+      </c>
+      <c r="M35" s="3">
         <v>400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>200</v>
       </c>
-      <c r="N35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1961,49 +2040,52 @@
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E38" s="2">
         <v>45230</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45046</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44865</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44681</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44500</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44316</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44135</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43951</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43769</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43585</v>
       </c>
-      <c r="N38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2013,8 +2095,11 @@
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2032,8 +2117,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2051,37 +2137,38 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>800</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>3</v>
+      <c r="L41" s="3">
+        <v>0</v>
       </c>
       <c r="M41" s="3" t="s">
         <v>3</v>
@@ -2098,8 +2185,11 @@
       <c r="Q41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2110,17 +2200,17 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>2100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>1200</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2136,8 +2226,8 @@
       <c r="N42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
+      <c r="O42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P42" s="3">
         <v>0</v>
@@ -2145,38 +2235,41 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E43" s="3">
         <v>7500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>7000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>14600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>10900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>11800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>5500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>5000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>600</v>
       </c>
-      <c r="L43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2192,37 +2285,40 @@
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>200</v>
+      </c>
+      <c r="E44" s="3">
         <v>1000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>200</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>3</v>
+      <c r="L44" s="3">
+        <v>0</v>
       </c>
       <c r="M44" s="3" t="s">
         <v>3</v>
@@ -2239,38 +2335,41 @@
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
         <v>800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>100</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2286,38 +2385,41 @@
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E46" s="3">
         <v>10500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>8700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>23300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>22200</v>
-      </c>
-      <c r="I46" s="3">
-        <v>6500</v>
       </c>
       <c r="J46" s="3">
         <v>6500</v>
       </c>
       <c r="K46" s="3">
+        <v>6500</v>
+      </c>
+      <c r="L46" s="3">
         <v>700</v>
       </c>
-      <c r="L46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,38 +2435,41 @@
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
+        <v>0</v>
+      </c>
+      <c r="F47" s="3">
         <v>400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7900</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>300</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2380,37 +2485,40 @@
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>700</v>
+      </c>
+      <c r="E48" s="3">
         <v>900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>1100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1200</v>
-      </c>
-      <c r="I48" s="3">
-        <v>100</v>
       </c>
       <c r="J48" s="3">
         <v>100</v>
       </c>
       <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="s">
         <v>3</v>
@@ -2427,8 +2535,11 @@
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2456,8 +2567,8 @@
       <c r="K49" s="3">
         <v>0</v>
       </c>
-      <c r="L49" s="3" t="s">
-        <v>3</v>
+      <c r="L49" s="3">
+        <v>0</v>
       </c>
       <c r="M49" s="3" t="s">
         <v>3</v>
@@ -2474,8 +2585,11 @@
       <c r="Q49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2521,8 +2635,11 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2568,37 +2685,40 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E52" s="3">
         <v>0</v>
       </c>
       <c r="F52" s="3">
+        <v>0</v>
+      </c>
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>600</v>
       </c>
-      <c r="I52" s="3">
-        <v>0</v>
-      </c>
       <c r="J52" s="3">
         <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
       </c>
-      <c r="L52" s="3" t="s">
-        <v>3</v>
+      <c r="L52" s="3">
+        <v>0</v>
       </c>
       <c r="M52" s="3" t="s">
         <v>3</v>
@@ -2615,8 +2735,11 @@
       <c r="Q52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2662,38 +2785,41 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E54" s="3">
         <v>11400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>27500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>28200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>11900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1000</v>
       </c>
-      <c r="L54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2709,8 +2835,11 @@
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2728,8 +2857,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2747,8 +2877,9 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -2765,7 +2896,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I57" s="3">
         <v>100</v>
@@ -2774,10 +2905,10 @@
         <v>100</v>
       </c>
       <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3" t="s">
         <v>3</v>
@@ -2794,26 +2925,29 @@
       <c r="Q57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3">
-        <v>0</v>
+      <c r="D58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E58" s="3">
+        <v>0</v>
+      </c>
+      <c r="F58" s="3">
         <v>400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>2800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4200</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2829,8 +2963,8 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
+      <c r="N58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O58" s="3">
         <v>0</v>
@@ -2841,38 +2975,41 @@
       <c r="Q58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E59" s="3">
         <v>6700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>300</v>
       </c>
-      <c r="L59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2888,38 +3025,41 @@
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E60" s="3">
         <v>6700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>6100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>4000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>4600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>300</v>
       </c>
-      <c r="L60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2935,8 +3075,11 @@
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -2982,29 +3125,32 @@
       <c r="Q61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>300</v>
+      </c>
+      <c r="E62" s="3">
         <v>400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1800</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3020,8 +3166,8 @@
       <c r="N62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O62" s="3">
-        <v>0</v>
+      <c r="O62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P62" s="3">
         <v>0</v>
@@ -3029,8 +3175,11 @@
       <c r="Q62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3076,8 +3225,11 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3123,8 +3275,11 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3170,38 +3325,41 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E66" s="3">
         <v>7200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>400</v>
       </c>
-      <c r="L66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3217,8 +3375,11 @@
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3236,8 +3397,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3283,8 +3445,11 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3495,11 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3377,8 +3545,11 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3424,38 +3595,41 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-17800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-15000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-8500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>8400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>600</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3645,11 @@
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3518,8 +3695,11 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3565,8 +3745,11 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3612,38 +3795,41 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50000</v>
+      </c>
+      <c r="E76" s="3">
         <v>4200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>3500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>22100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>9500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>600</v>
       </c>
-      <c r="L76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,8 +3845,11 @@
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3706,49 +3895,52 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45412</v>
+      </c>
+      <c r="E80" s="2">
         <v>45230</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45046</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44865</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44681</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44500</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44316</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44135</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43951</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43769</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43585</v>
       </c>
-      <c r="N80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="O80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3758,44 +3950,47 @@
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-15800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-9400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-6500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-16800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-5200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3500</v>
       </c>
-      <c r="K81" s="3">
-        <v>0</v>
-      </c>
       <c r="L81" s="3">
+        <v>0</v>
+      </c>
+      <c r="M81" s="3">
         <v>400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>200</v>
       </c>
-      <c r="N81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3805,8 +4000,11 @@
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3824,8 +4022,9 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -3836,28 +4035,28 @@
         <v>100</v>
       </c>
       <c r="F83" s="3">
+        <v>100</v>
+      </c>
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
-        <v>0</v>
-      </c>
       <c r="H83" s="3">
+        <v>0</v>
+      </c>
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
-        <v>0</v>
-      </c>
-      <c r="J83" s="3" t="s">
-        <v>3</v>
+      <c r="J83" s="3">
+        <v>0</v>
       </c>
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
@@ -3871,8 +4070,11 @@
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3918,8 +4120,11 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3965,8 +4170,11 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4012,8 +4220,11 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4059,8 +4270,11 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4106,41 +4320,44 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-50900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-5500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-8900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-4300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-4800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3">
         <v>-100</v>
       </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4153,8 +4370,11 @@
       <c r="Q89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4172,8 +4392,9 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4187,11 +4408,11 @@
         <v>0</v>
       </c>
       <c r="G91" s="3">
+        <v>0</v>
+      </c>
+      <c r="H91" s="3">
         <v>-300</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
@@ -4204,8 +4425,8 @@
       <c r="L91" s="3">
         <v>0</v>
       </c>
-      <c r="M91" s="3" t="s">
-        <v>3</v>
+      <c r="M91" s="3">
+        <v>0</v>
       </c>
       <c r="N91" s="3" t="s">
         <v>3</v>
@@ -4219,8 +4440,11 @@
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4266,8 +4490,11 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4313,40 +4540,43 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E94" s="3">
         <v>1300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1500</v>
       </c>
-      <c r="I94" s="3">
-        <v>0</v>
-      </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
+      <c r="J94" s="3">
+        <v>0</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3">
-        <v>0</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3">
+        <v>0</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
@@ -4360,8 +4590,11 @@
       <c r="Q94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4379,8 +4612,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4426,8 +4660,11 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4473,8 +4710,11 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4520,8 +4760,11 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4567,41 +4810,44 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>50600</v>
+      </c>
+      <c r="E100" s="3">
         <v>3200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>3600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>12800</v>
       </c>
-      <c r="I100" s="3">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
+      <c r="J100" s="3">
+        <v>0</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3">
         <v>100</v>
       </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4614,40 +4860,43 @@
       <c r="Q100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-200</v>
       </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
       <c r="F101" s="3">
         <v>0</v>
       </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>-400</v>
-      </c>
-      <c r="H101" s="3">
-        <v>100</v>
       </c>
       <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>100</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -4661,41 +4910,44 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>6600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-100</v>
       </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3">
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3">
         <v>-100</v>
       </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4706,6 +4958,9 @@
         <v>3</v>
       </c>
       <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
   <si>
     <t>JZXN</t>
   </si>
@@ -662,14 +662,11 @@
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -695,22 +692,22 @@
         <v>45412</v>
       </c>
       <c r="E7" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F7" s="2">
         <v>45230</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45138</v>
+      </c>
+      <c r="H7" s="2">
         <v>45046</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>44957</v>
+      </c>
+      <c r="J7" s="2">
         <v>44865</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44681</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44500</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44316</v>
       </c>
       <c r="K7" s="2">
         <v>44135</v>
@@ -742,25 +739,25 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>2300</v>
+        <v>1100</v>
       </c>
       <c r="E8" s="3">
-        <v>5900</v>
-      </c>
-      <c r="F8" s="3">
-        <v>600</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5900</v>
+        <v>1100</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H8" s="3">
-        <v>4100</v>
+        <v>300</v>
       </c>
       <c r="I8" s="3">
-        <v>9300</v>
-      </c>
-      <c r="J8" s="3">
-        <v>4600</v>
+        <v>300</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K8" s="3">
         <v>8200</v>
@@ -792,25 +789,25 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>2300</v>
+        <v>2400</v>
       </c>
       <c r="E9" s="3">
-        <v>4600</v>
-      </c>
-      <c r="F9" s="3">
-        <v>800</v>
-      </c>
-      <c r="G9" s="3">
-        <v>6300</v>
+        <v>2400</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H9" s="3">
-        <v>3600</v>
+        <v>600</v>
       </c>
       <c r="I9" s="3">
-        <v>4900</v>
-      </c>
-      <c r="J9" s="3">
-        <v>1500</v>
+        <v>600</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K9" s="3">
         <v>2200</v>
@@ -842,25 +839,25 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="E10" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F10" s="3">
-        <v>-200</v>
-      </c>
-      <c r="G10" s="3">
-        <v>-400</v>
+        <v>-1300</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H10" s="3">
-        <v>500</v>
+        <v>-300</v>
       </c>
       <c r="I10" s="3">
-        <v>4400</v>
-      </c>
-      <c r="J10" s="3">
-        <v>3100</v>
+        <v>-300</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K10" s="3">
         <v>6000</v>
@@ -1011,26 +1008,26 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1074,13 +1071,13 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1129,25 +1126,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>18100</v>
+        <v>9100</v>
       </c>
       <c r="E17" s="3">
-        <v>15400</v>
-      </c>
-      <c r="F17" s="3">
-        <v>6700</v>
-      </c>
-      <c r="G17" s="3">
-        <v>22600</v>
+        <v>9100</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H17" s="3">
-        <v>10200</v>
+        <v>3400</v>
       </c>
       <c r="I17" s="3">
-        <v>8200</v>
-      </c>
-      <c r="J17" s="3">
-        <v>2800</v>
+        <v>3400</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K17" s="3">
         <v>3800</v>
@@ -1179,25 +1176,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-15800</v>
+        <v>-7900</v>
       </c>
       <c r="E18" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="F18" s="3">
-        <v>-6100</v>
-      </c>
-      <c r="G18" s="3">
-        <v>-16700</v>
+        <v>-7900</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H18" s="3">
-        <v>-6100</v>
+        <v>-3100</v>
       </c>
       <c r="I18" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J18" s="3">
-        <v>1800</v>
+        <v>-3100</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K18" s="3">
         <v>4400</v>
@@ -1252,22 +1249,22 @@
         <v>0</v>
       </c>
       <c r="E20" s="3">
-        <v>100</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0</v>
-      </c>
-      <c r="G20" s="3">
-        <v>1700</v>
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H20" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3">
-        <v>0</v>
+      <c r="J20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -1299,25 +1296,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-15800</v>
+        <v>-7900</v>
       </c>
       <c r="E21" s="3">
-        <v>-9400</v>
+        <v>-7900</v>
       </c>
       <c r="F21" s="3">
-        <v>-6000</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>-14800</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
-        <v>-4600</v>
+        <v>-3000</v>
       </c>
       <c r="I21" s="3">
-        <v>1200</v>
+        <v>-3000</v>
       </c>
       <c r="J21" s="3">
-        <v>1800</v>
+        <v>100</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1349,22 +1346,22 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="3">
         <v>100</v>
       </c>
-      <c r="E22" s="3">
-        <v>300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>200</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>500</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
+      <c r="I22" s="3">
+        <v>100</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
@@ -1399,25 +1396,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-15900</v>
+        <v>-7900</v>
       </c>
       <c r="E23" s="3">
-        <v>-9800</v>
-      </c>
-      <c r="F23" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="G23" s="3">
-        <v>-16400</v>
+        <v>-7900</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H23" s="3">
-        <v>-5100</v>
+        <v>-3200</v>
       </c>
       <c r="I23" s="3">
-        <v>1100</v>
-      </c>
-      <c r="J23" s="3">
-        <v>1800</v>
+        <v>-3200</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K23" s="3">
         <v>4400</v>
@@ -1448,26 +1445,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H24" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I24" s="3">
-        <v>500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>400</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K24" s="3">
         <v>1000</v>
@@ -1549,25 +1546,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-15900</v>
+        <v>-7900</v>
       </c>
       <c r="E26" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="F26" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>-16400</v>
+        <v>-7900</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H26" s="3">
-        <v>-5300</v>
+        <v>-3200</v>
       </c>
       <c r="I26" s="3">
-        <v>600</v>
-      </c>
-      <c r="J26" s="3">
-        <v>1300</v>
+        <v>-3200</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K26" s="3">
         <v>3400</v>
@@ -1599,25 +1596,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-15900</v>
+        <v>-7900</v>
       </c>
       <c r="E27" s="3">
-        <v>-9900</v>
-      </c>
-      <c r="F27" s="3">
-        <v>-6300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>-16300</v>
+        <v>-7900</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H27" s="3">
-        <v>-5200</v>
+        <v>-3300</v>
       </c>
       <c r="I27" s="3">
-        <v>600</v>
-      </c>
-      <c r="J27" s="3">
-        <v>1300</v>
+        <v>-3300</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K27" s="3">
         <v>3500</v>
@@ -1699,25 +1696,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-200</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-500</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>-100</v>
       </c>
       <c r="I29" s="3">
-        <v>200</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
+        <v>-100</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1852,22 +1849,22 @@
         <v>0</v>
       </c>
       <c r="E32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-1700</v>
+        <v>0</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H32" s="3">
-        <v>-1400</v>
+        <v>0</v>
       </c>
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3">
-        <v>0</v>
+      <c r="J32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
@@ -1899,25 +1896,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-15800</v>
+        <v>-7900</v>
       </c>
       <c r="E33" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="F33" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G33" s="3">
-        <v>-16800</v>
+        <v>-7900</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H33" s="3">
-        <v>-5200</v>
+        <v>-3300</v>
       </c>
       <c r="I33" s="3">
-        <v>800</v>
-      </c>
-      <c r="J33" s="3">
-        <v>1300</v>
+        <v>-3300</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K33" s="3">
         <v>3500</v>
@@ -1999,25 +1996,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-15800</v>
+        <v>-7900</v>
       </c>
       <c r="E35" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="F35" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G35" s="3">
-        <v>-16800</v>
+        <v>-7900</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H35" s="3">
-        <v>-5200</v>
+        <v>-3300</v>
       </c>
       <c r="I35" s="3">
-        <v>800</v>
-      </c>
-      <c r="J35" s="3">
-        <v>1300</v>
+        <v>-3300</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K35" s="3">
         <v>3500</v>
@@ -2057,22 +2054,22 @@
         <v>45412</v>
       </c>
       <c r="E38" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F38" s="2">
         <v>45230</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45138</v>
+      </c>
+      <c r="H38" s="2">
         <v>45046</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>44957</v>
+      </c>
+      <c r="J38" s="2">
         <v>44865</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44681</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44500</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44316</v>
       </c>
       <c r="K38" s="2">
         <v>44135</v>
@@ -2147,22 +2144,22 @@
         <v>300</v>
       </c>
       <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
         <v>1200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H41" s="3">
         <v>800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
+        <v>800</v>
+      </c>
+      <c r="J41" s="3">
         <v>2300</v>
-      </c>
-      <c r="H41" s="3">
-        <v>6000</v>
-      </c>
-      <c r="I41" s="3">
-        <v>7400</v>
-      </c>
-      <c r="J41" s="3">
-        <v>700</v>
       </c>
       <c r="K41" s="3">
         <v>800</v>
@@ -2203,16 +2200,16 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>600</v>
-      </c>
-      <c r="H42" s="3">
-        <v>2100</v>
-      </c>
-      <c r="I42" s="3">
-        <v>1200</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
       </c>
       <c r="K42" s="3" t="s">
         <v>3</v>
@@ -2244,25 +2241,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>54900</v>
+        <v>3200</v>
       </c>
       <c r="E43" s="3">
-        <v>7500</v>
+        <v>3200</v>
       </c>
       <c r="F43" s="3">
-        <v>7000</v>
+        <v>6200</v>
       </c>
       <c r="G43" s="3">
-        <v>14600</v>
+        <v>6200</v>
       </c>
       <c r="H43" s="3">
-        <v>10900</v>
+        <v>5400</v>
       </c>
       <c r="I43" s="3">
-        <v>11800</v>
+        <v>5400</v>
       </c>
       <c r="J43" s="3">
-        <v>5500</v>
+        <v>6900</v>
       </c>
       <c r="K43" s="3">
         <v>5000</v>
@@ -2297,22 +2294,22 @@
         <v>200</v>
       </c>
       <c r="E44" s="3">
+        <v>200</v>
+      </c>
+      <c r="F44" s="3">
         <v>1000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
+        <v>1000</v>
+      </c>
+      <c r="H44" s="3">
         <v>500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
+        <v>500</v>
+      </c>
+      <c r="J44" s="3">
         <v>600</v>
-      </c>
-      <c r="H44" s="3">
-        <v>400</v>
-      </c>
-      <c r="I44" s="3">
-        <v>300</v>
-      </c>
-      <c r="J44" s="3">
-        <v>100</v>
       </c>
       <c r="K44" s="3">
         <v>200</v>
@@ -2344,25 +2341,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="E45" s="3">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="F45" s="3">
-        <v>300</v>
+        <v>2000</v>
       </c>
       <c r="G45" s="3">
-        <v>700</v>
+        <v>2000</v>
       </c>
       <c r="H45" s="3">
-        <v>4000</v>
+        <v>1300</v>
       </c>
       <c r="I45" s="3">
-        <v>1600</v>
+        <v>1300</v>
       </c>
       <c r="J45" s="3">
-        <v>200</v>
+        <v>1800</v>
       </c>
       <c r="K45" s="3">
         <v>600</v>
@@ -2397,22 +2394,22 @@
         <v>55500</v>
       </c>
       <c r="E46" s="3">
+        <v>55500</v>
+      </c>
+      <c r="F46" s="3">
         <v>10500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
+        <v>10500</v>
+      </c>
+      <c r="H46" s="3">
         <v>8700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
+        <v>8700</v>
+      </c>
+      <c r="J46" s="3">
         <v>12200</v>
-      </c>
-      <c r="H46" s="3">
-        <v>23300</v>
-      </c>
-      <c r="I46" s="3">
-        <v>22200</v>
-      </c>
-      <c r="J46" s="3">
-        <v>6500</v>
       </c>
       <c r="K46" s="3">
         <v>6500</v>
@@ -2446,23 +2443,23 @@
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>400</v>
-      </c>
-      <c r="G47" s="3">
-        <v>1600</v>
-      </c>
-      <c r="H47" s="3">
-        <v>2700</v>
-      </c>
-      <c r="I47" s="3">
-        <v>4100</v>
-      </c>
-      <c r="J47" s="3">
-        <v>7900</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K47" s="3">
         <v>5300</v>
@@ -2497,22 +2494,22 @@
         <v>700</v>
       </c>
       <c r="E48" s="3">
+        <v>700</v>
+      </c>
+      <c r="F48" s="3">
         <v>900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
+        <v>900</v>
+      </c>
+      <c r="H48" s="3">
         <v>1200</v>
-      </c>
-      <c r="G48" s="3">
-        <v>1400</v>
-      </c>
-      <c r="H48" s="3">
-        <v>1100</v>
       </c>
       <c r="I48" s="3">
         <v>1200</v>
       </c>
       <c r="J48" s="3">
-        <v>100</v>
+        <v>1400</v>
       </c>
       <c r="K48" s="3">
         <v>100</v>
@@ -2697,22 +2694,22 @@
         <v>100</v>
       </c>
       <c r="E52" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F52" s="3">
         <v>0</v>
       </c>
       <c r="G52" s="3">
+        <v>0</v>
+      </c>
+      <c r="H52" s="3">
+        <v>0</v>
+      </c>
+      <c r="I52" s="3">
+        <v>0</v>
+      </c>
+      <c r="J52" s="3">
         <v>100</v>
-      </c>
-      <c r="H52" s="3">
-        <v>500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>0</v>
       </c>
       <c r="K52" s="3">
         <v>0</v>
@@ -2797,22 +2794,22 @@
         <v>56200</v>
       </c>
       <c r="E54" s="3">
+        <v>56200</v>
+      </c>
+      <c r="F54" s="3">
         <v>11400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>11400</v>
+      </c>
+      <c r="H54" s="3">
         <v>10400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>10400</v>
+      </c>
+      <c r="J54" s="3">
         <v>15300</v>
-      </c>
-      <c r="H54" s="3">
-        <v>27500</v>
-      </c>
-      <c r="I54" s="3">
-        <v>28200</v>
-      </c>
-      <c r="J54" s="3">
-        <v>14500</v>
       </c>
       <c r="K54" s="3">
         <v>11900</v>
@@ -2899,10 +2896,10 @@
         <v>0</v>
       </c>
       <c r="I57" s="3">
-        <v>100</v>
-      </c>
-      <c r="J57" s="3">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K57" s="3">
         <v>100</v>
@@ -2933,26 +2930,26 @@
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>3</v>
+      <c r="D58" s="3">
+        <v>200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F58" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G58" s="3">
-        <v>2800</v>
+        <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>4200</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>3</v>
+        <v>800</v>
+      </c>
+      <c r="I58" s="3">
+        <v>800</v>
+      </c>
+      <c r="J58" s="3">
+        <v>3200</v>
       </c>
       <c r="K58" s="3" t="s">
         <v>3</v>
@@ -2984,25 +2981,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5700</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
-        <v>6700</v>
+        <v>2500</v>
       </c>
       <c r="F59" s="3">
-        <v>5600</v>
+        <v>3600</v>
       </c>
       <c r="G59" s="3">
-        <v>5500</v>
+        <v>3600</v>
       </c>
       <c r="H59" s="3">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="I59" s="3">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="J59" s="3">
-        <v>4600</v>
+        <v>3800</v>
       </c>
       <c r="K59" s="3">
         <v>3600</v>
@@ -3037,22 +3034,22 @@
         <v>5700</v>
       </c>
       <c r="E60" s="3">
+        <v>5700</v>
+      </c>
+      <c r="F60" s="3">
         <v>6700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
+        <v>6700</v>
+      </c>
+      <c r="H60" s="3">
         <v>6100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
+        <v>6100</v>
+      </c>
+      <c r="J60" s="3">
         <v>8300</v>
-      </c>
-      <c r="H60" s="3">
-        <v>9700</v>
-      </c>
-      <c r="I60" s="3">
-        <v>4000</v>
-      </c>
-      <c r="J60" s="3">
-        <v>4600</v>
       </c>
       <c r="K60" s="3">
         <v>3700</v>
@@ -3084,25 +3081,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="J61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="K61" s="3">
         <v>0</v>
@@ -3133,26 +3130,26 @@
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
-        <v>400</v>
-      </c>
-      <c r="F62" s="3">
-        <v>700</v>
-      </c>
-      <c r="G62" s="3">
-        <v>1000</v>
+      <c r="D62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>1600</v>
+        <v>100</v>
       </c>
       <c r="I62" s="3">
-        <v>1800</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>3</v>
+        <v>100</v>
+      </c>
+      <c r="J62" s="3">
+        <v>100</v>
       </c>
       <c r="K62" s="3" t="s">
         <v>3</v>
@@ -3334,25 +3331,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6200</v>
+        <v>6100</v>
       </c>
       <c r="E66" s="3">
-        <v>7200</v>
+        <v>6100</v>
       </c>
       <c r="F66" s="3">
-        <v>6900</v>
+        <v>7100</v>
       </c>
       <c r="G66" s="3">
-        <v>9400</v>
+        <v>7100</v>
       </c>
       <c r="H66" s="3">
-        <v>11500</v>
+        <v>6800</v>
       </c>
       <c r="I66" s="3">
-        <v>6100</v>
+        <v>6800</v>
       </c>
       <c r="J66" s="3">
-        <v>5000</v>
+        <v>9200</v>
       </c>
       <c r="K66" s="3">
         <v>4100</v>
@@ -3607,22 +3604,22 @@
         <v>-33600</v>
       </c>
       <c r="E72" s="3">
+        <v>-33600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-17800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="H72" s="3">
         <v>-15000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="J72" s="3">
         <v>-8500</v>
-      </c>
-      <c r="H72" s="3">
-        <v>3100</v>
-      </c>
-      <c r="I72" s="3">
-        <v>8400</v>
-      </c>
-      <c r="J72" s="3">
-        <v>8900</v>
       </c>
       <c r="K72" s="3">
         <v>7500</v>
@@ -3807,22 +3804,22 @@
         <v>50000</v>
       </c>
       <c r="E76" s="3">
+        <v>50000</v>
+      </c>
+      <c r="F76" s="3">
         <v>4200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H76" s="3">
         <v>3500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>3500</v>
+      </c>
+      <c r="J76" s="3">
         <v>5900</v>
-      </c>
-      <c r="H76" s="3">
-        <v>16100</v>
-      </c>
-      <c r="I76" s="3">
-        <v>22100</v>
-      </c>
-      <c r="J76" s="3">
-        <v>9500</v>
       </c>
       <c r="K76" s="3">
         <v>7800</v>
@@ -3912,22 +3909,22 @@
         <v>45412</v>
       </c>
       <c r="E80" s="2">
+        <v>45322</v>
+      </c>
+      <c r="F80" s="2">
         <v>45230</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45138</v>
+      </c>
+      <c r="H80" s="2">
         <v>45046</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>44957</v>
+      </c>
+      <c r="J80" s="2">
         <v>44865</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44681</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44500</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44316</v>
       </c>
       <c r="K80" s="2">
         <v>44135</v>
@@ -3959,25 +3956,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-15800</v>
+        <v>-7900</v>
       </c>
       <c r="E81" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="F81" s="3">
-        <v>-6500</v>
-      </c>
-      <c r="G81" s="3">
-        <v>-16800</v>
+        <v>-7900</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H81" s="3">
-        <v>-5200</v>
+        <v>-3300</v>
       </c>
       <c r="I81" s="3">
-        <v>800</v>
-      </c>
-      <c r="J81" s="3">
-        <v>1300</v>
+        <v>-3300</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K81" s="3">
         <v>3500</v>
@@ -4034,14 +4031,14 @@
       <c r="E83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H83" s="3">
         <v>100</v>
-      </c>
-      <c r="G83" s="3">
-        <v>200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
       </c>
       <c r="I83" s="3">
         <v>100</v>
@@ -4329,25 +4326,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-50900</v>
+        <v>-25400</v>
       </c>
       <c r="E89" s="3">
-        <v>-5500</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2700</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-8900</v>
+        <v>-25400</v>
+      </c>
+      <c r="F89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H89" s="3">
-        <v>-4300</v>
+        <v>-1400</v>
       </c>
       <c r="I89" s="3">
-        <v>-4800</v>
-      </c>
-      <c r="J89" s="3">
-        <v>-100</v>
+        <v>-1400</v>
+      </c>
+      <c r="J89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K89" s="3" t="s">
         <v>3</v>
@@ -4398,26 +4395,26 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H91" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="J91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -4549,25 +4546,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-700</v>
+        <v>-400</v>
       </c>
       <c r="E94" s="3">
-        <v>1300</v>
-      </c>
-      <c r="F94" s="3">
-        <v>800</v>
-      </c>
-      <c r="G94" s="3">
-        <v>200</v>
+        <v>-400</v>
+      </c>
+      <c r="F94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H94" s="3">
-        <v>-900</v>
+        <v>400</v>
       </c>
       <c r="I94" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="J94" s="3">
-        <v>0</v>
+        <v>400</v>
+      </c>
+      <c r="J94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K94" s="3" t="s">
         <v>3</v>
@@ -4618,26 +4615,26 @@
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -4819,25 +4816,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>50600</v>
+        <v>25300</v>
       </c>
       <c r="E100" s="3">
-        <v>3200</v>
-      </c>
-      <c r="F100" s="3">
-        <v>300</v>
-      </c>
-      <c r="G100" s="3">
-        <v>3600</v>
+        <v>25300</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H100" s="3">
-        <v>4200</v>
+        <v>200</v>
       </c>
       <c r="I100" s="3">
-        <v>12800</v>
-      </c>
-      <c r="J100" s="3">
-        <v>0</v>
+        <v>200</v>
+      </c>
+      <c r="J100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K100" s="3" t="s">
         <v>3</v>
@@ -4869,25 +4866,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="E101" s="3">
+        <v>0</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H101" s="3">
         <v>-200</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>-400</v>
-      </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>-200</v>
       </c>
       <c r="J101" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -4919,25 +4916,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-900</v>
+        <v>-500</v>
       </c>
       <c r="E102" s="3">
-        <v>-1200</v>
+        <v>-500</v>
       </c>
       <c r="F102" s="3">
-        <v>-1500</v>
+        <v>0</v>
       </c>
       <c r="G102" s="3">
-        <v>-5000</v>
+        <v>0</v>
       </c>
       <c r="H102" s="3">
-        <v>-1400</v>
+        <v>-800</v>
       </c>
       <c r="I102" s="3">
-        <v>6600</v>
+        <v>-800</v>
       </c>
       <c r="J102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
   <si>
     <t>JZXN</t>
   </si>
@@ -656,235 +656,261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="9.140625" style="1"/>
+    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F7" s="2">
         <v>45412</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45322</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45230</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45138</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45046</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44957</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44865</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44135</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43951</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43769</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43585</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3">
         <v>1100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1100</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H8" s="3">
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3">
         <v>300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>300</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
         <v>8200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="E9" s="3">
+        <v>-1800</v>
+      </c>
+      <c r="F9" s="3">
         <v>2400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2400</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H9" s="3">
+        <v>-600</v>
+      </c>
+      <c r="I9" s="3">
+        <v>-600</v>
+      </c>
+      <c r="J9" s="3">
         <v>600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>600</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3">
         <v>2200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>200</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1300</v>
+      </c>
+      <c r="F10" s="3">
         <v>-1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>-1300</v>
       </c>
-      <c r="F10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H10" s="3">
+        <v>300</v>
+      </c>
+      <c r="I10" s="3">
+        <v>300</v>
+      </c>
+      <c r="J10" s="3">
         <v>-300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>-300</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3">
         <v>6000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>300</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,8 +929,10 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -953,8 +981,14 @@
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1003,8 +1037,14 @@
       <c r="R13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1029,11 +1069,11 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1053,8 +1093,14 @@
       <c r="R14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1071,19 +1117,19 @@
         <v>0</v>
       </c>
       <c r="H15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1103,8 +1149,14 @@
       <c r="R15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3">
+        <v>0</v>
+      </c>
+      <c r="T15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1120,108 +1172,122 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>19500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>19500</v>
+      </c>
+      <c r="F17" s="3">
         <v>9100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>9100</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H17" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="I17" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="J17" s="3">
         <v>3400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>3400</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3">
         <v>3800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>300</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F18" s="3">
         <v>-7900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-7900</v>
       </c>
-      <c r="F18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H18" s="3">
+        <v>800</v>
+      </c>
+      <c r="I18" s="3">
+        <v>800</v>
+      </c>
+      <c r="J18" s="3">
         <v>-3100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>-3100</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3">
         <v>4400</v>
       </c>
-      <c r="L18" s="3">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
+        <v>0</v>
+      </c>
+      <c r="O18" s="3">
         <v>500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>300</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1240,8 +1306,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1251,11 +1319,11 @@
       <c r="E20" s="3">
         <v>0</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
+      <c r="F20" s="3">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3">
+        <v>0</v>
       </c>
       <c r="H20" s="3">
         <v>0</v>
@@ -1263,14 +1331,14 @@
       <c r="I20" s="3">
         <v>0</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>3</v>
+      <c r="J20" s="3">
+        <v>0</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
+      <c r="L20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
@@ -1278,11 +1346,11 @@
       <c r="N20" s="3">
         <v>0</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
+      <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
+        <v>0</v>
       </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
@@ -1290,58 +1358,70 @@
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F21" s="3">
         <v>-7900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-7900</v>
       </c>
-      <c r="F21" s="3">
-        <v>0</v>
-      </c>
-      <c r="G21" s="3">
-        <v>0</v>
-      </c>
       <c r="H21" s="3">
+        <v>800</v>
+      </c>
+      <c r="I21" s="3">
+        <v>800</v>
+      </c>
+      <c r="J21" s="3">
         <v>-3000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>-3000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>100</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O21" s="3">
         <v>500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>300</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1351,24 +1431,24 @@
       <c r="E22" s="3">
         <v>0</v>
       </c>
-      <c r="F22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
+      <c r="F22" s="3">
+        <v>0</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3">
+        <v>0</v>
+      </c>
+      <c r="I22" s="3">
+        <v>0</v>
+      </c>
+      <c r="J22" s="3">
         <v>100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>100</v>
       </c>
-      <c r="J22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1378,11 +1458,11 @@
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1390,58 +1470,70 @@
       <c r="R22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F23" s="3">
         <v>-7900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-7900</v>
       </c>
-      <c r="F23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H23" s="3">
+        <v>800</v>
+      </c>
+      <c r="I23" s="3">
+        <v>800</v>
+      </c>
+      <c r="J23" s="3">
         <v>-3200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>-3200</v>
       </c>
-      <c r="J23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3">
         <v>4400</v>
       </c>
-      <c r="L23" s="3">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
+        <v>0</v>
+      </c>
+      <c r="O23" s="3">
         <v>500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>300</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1463,35 +1555,41 @@
       <c r="I24" s="3">
         <v>0</v>
       </c>
-      <c r="J24" s="3" t="s">
-        <v>3</v>
+      <c r="J24" s="3">
+        <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1540,108 +1638,126 @@
       <c r="R25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-19900</v>
+      </c>
+      <c r="F26" s="3">
         <v>-7900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-7900</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H26" s="3">
+        <v>800</v>
+      </c>
+      <c r="I26" s="3">
+        <v>800</v>
+      </c>
+      <c r="J26" s="3">
         <v>-3200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>-3200</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3">
         <v>3400</v>
       </c>
-      <c r="L26" s="3">
-        <v>0</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
+        <v>0</v>
+      </c>
+      <c r="O26" s="3">
         <v>400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>200</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F27" s="3">
         <v>-7900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-7900</v>
       </c>
-      <c r="F27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I27" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J27" s="3">
         <v>-3300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-3300</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3">
         <v>3500</v>
       </c>
-      <c r="L27" s="3">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
+        <v>0</v>
+      </c>
+      <c r="O27" s="3">
         <v>400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>200</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1690,16 +1806,22 @@
       <c r="R28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-1700</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -1708,22 +1830,22 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I29" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="J29" s="3">
         <v>-100</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-100</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -1740,8 +1862,14 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3">
+        <v>0</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1790,8 +1918,14 @@
       <c r="R30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1840,8 +1974,14 @@
       <c r="R31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1851,11 +1991,11 @@
       <c r="E32" s="3">
         <v>0</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
+      <c r="F32" s="3">
+        <v>0</v>
+      </c>
+      <c r="G32" s="3">
+        <v>0</v>
       </c>
       <c r="H32" s="3">
         <v>0</v>
@@ -1863,14 +2003,14 @@
       <c r="I32" s="3">
         <v>0</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>3</v>
+      <c r="J32" s="3">
+        <v>0</v>
       </c>
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
+      <c r="L32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
@@ -1878,11 +2018,11 @@
       <c r="N32" s="3">
         <v>0</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
+      <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0</v>
       </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
@@ -1890,58 +2030,70 @@
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F33" s="3">
         <v>-7900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-7900</v>
       </c>
-      <c r="F33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I33" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J33" s="3">
         <v>-3300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-3300</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3">
         <v>3500</v>
       </c>
-      <c r="L33" s="3">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
+        <v>0</v>
+      </c>
+      <c r="O33" s="3">
         <v>400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>200</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1990,113 +2142,131 @@
       <c r="R34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F35" s="3">
         <v>-7900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-7900</v>
       </c>
-      <c r="F35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I35" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J35" s="3">
         <v>-3300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-3300</v>
       </c>
-      <c r="J35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3">
         <v>3500</v>
       </c>
-      <c r="L35" s="3">
-        <v>0</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
+        <v>0</v>
+      </c>
+      <c r="O35" s="3">
         <v>400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>200</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F38" s="2">
         <v>45412</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45322</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45230</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45138</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45046</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44957</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44865</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44135</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43951</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43769</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43585</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2115,8 +2285,10 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2135,43 +2307,45 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>900</v>
+      </c>
+      <c r="F41" s="3">
         <v>300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>300</v>
       </c>
-      <c r="F41" s="3">
-        <v>1200</v>
-      </c>
-      <c r="G41" s="3">
-        <v>1200</v>
-      </c>
       <c r="H41" s="3">
+        <v>700</v>
+      </c>
+      <c r="I41" s="3">
+        <v>700</v>
+      </c>
+      <c r="J41" s="3">
         <v>800</v>
-      </c>
-      <c r="I41" s="3">
-        <v>800</v>
-      </c>
-      <c r="J41" s="3">
-        <v>2300</v>
       </c>
       <c r="K41" s="3">
         <v>800</v>
       </c>
       <c r="L41" s="3">
-        <v>0</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N41" s="3" t="s">
-        <v>3</v>
+        <v>2300</v>
+      </c>
+      <c r="M41" s="3">
+        <v>800</v>
+      </c>
+      <c r="N41" s="3">
+        <v>0</v>
       </c>
       <c r="O41" s="3" t="s">
         <v>3</v>
@@ -2185,8 +2359,14 @@
       <c r="R41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2209,14 +2389,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>600</v>
       </c>
-      <c r="K42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2226,53 +2406,59 @@
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q42" s="3">
-        <v>0</v>
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F43" s="3">
         <v>3200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3200</v>
       </c>
-      <c r="F43" s="3">
-        <v>6200</v>
-      </c>
-      <c r="G43" s="3">
-        <v>6200</v>
-      </c>
       <c r="H43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="I43" s="3">
+        <v>1700</v>
+      </c>
+      <c r="J43" s="3">
         <v>5400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>5400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>6900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>600</v>
       </c>
-      <c r="M43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2285,43 +2471,49 @@
       <c r="R43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3">
         <v>200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>200</v>
       </c>
-      <c r="F44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="G44" s="3">
-        <v>1000</v>
-      </c>
-      <c r="H44" s="3">
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3">
         <v>500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>200</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N44" s="3" t="s">
-        <v>3</v>
+      <c r="N44" s="3">
+        <v>0</v>
       </c>
       <c r="O44" s="3" t="s">
         <v>3</v>
@@ -2335,44 +2527,50 @@
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>100</v>
+      </c>
+      <c r="E45" s="3">
+        <v>100</v>
+      </c>
+      <c r="F45" s="3">
         <v>1200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1200</v>
       </c>
-      <c r="F45" s="3">
-        <v>2000</v>
-      </c>
-      <c r="G45" s="3">
-        <v>2000</v>
-      </c>
       <c r="H45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="I45" s="3">
+        <v>8100</v>
+      </c>
+      <c r="J45" s="3">
         <v>1300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>100</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2385,44 +2583,50 @@
       <c r="R45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E46" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F46" s="3">
         <v>55500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>55500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>10500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>10500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>8700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>8700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>6500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>700</v>
       </c>
-      <c r="M46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2435,8 +2639,14 @@
       <c r="R46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2461,18 +2671,18 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>5300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>300</v>
       </c>
-      <c r="M47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2485,43 +2695,49 @@
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3">
+      <c r="D48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F48" s="3">
         <v>700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>700</v>
       </c>
-      <c r="F48" s="3">
-        <v>900</v>
-      </c>
-      <c r="G48" s="3">
-        <v>900</v>
-      </c>
-      <c r="H48" s="3">
+      <c r="H48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J48" s="3">
         <v>1200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>100</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N48" s="3" t="s">
-        <v>3</v>
+      <c r="N48" s="3">
+        <v>0</v>
       </c>
       <c r="O48" s="3" t="s">
         <v>3</v>
@@ -2535,8 +2751,14 @@
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2567,11 +2789,11 @@
       <c r="L49" s="3">
         <v>0</v>
       </c>
-      <c r="M49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N49" s="3" t="s">
-        <v>3</v>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
       </c>
       <c r="O49" s="3" t="s">
         <v>3</v>
@@ -2585,8 +2807,14 @@
       <c r="R49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2635,8 +2863,14 @@
       <c r="R50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2685,43 +2919,49 @@
       <c r="R51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="3">
         <v>100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>100</v>
       </c>
-      <c r="F52" s="3">
-        <v>0</v>
-      </c>
-      <c r="G52" s="3">
-        <v>0</v>
-      </c>
       <c r="H52" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="I52" s="3">
-        <v>0</v>
+        <v>900</v>
       </c>
       <c r="J52" s="3">
+        <v>0</v>
+      </c>
+      <c r="K52" s="3">
+        <v>0</v>
+      </c>
+      <c r="L52" s="3">
         <v>100</v>
       </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
-      <c r="L52" s="3">
-        <v>0</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N52" s="3" t="s">
-        <v>3</v>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
+        <v>0</v>
       </c>
       <c r="O52" s="3" t="s">
         <v>3</v>
@@ -2735,8 +2975,14 @@
       <c r="R52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2785,44 +3031,50 @@
       <c r="R53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>10600</v>
+      </c>
+      <c r="F54" s="3">
         <v>56200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>56200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>11400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>11400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>10400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>10400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>15300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>11900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>1000</v>
       </c>
-      <c r="M54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2835,8 +3087,14 @@
       <c r="R54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2855,8 +3113,10 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2875,16 +3135,18 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F57" s="3">
         <v>0</v>
@@ -2892,26 +3154,26 @@
       <c r="G57" s="3">
         <v>0</v>
       </c>
-      <c r="H57" s="3">
-        <v>0</v>
-      </c>
-      <c r="I57" s="3">
-        <v>0</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J57" s="3">
+        <v>0</v>
       </c>
       <c r="K57" s="3">
+        <v>0</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
         <v>100</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N57" s="3" t="s">
-        <v>3</v>
+      <c r="N57" s="3">
+        <v>0</v>
       </c>
       <c r="O57" s="3" t="s">
         <v>3</v>
@@ -2925,8 +3187,14 @@
       <c r="R57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2943,31 +3211,31 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
+        <v>0</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
+      </c>
+      <c r="J58" s="3">
         <v>800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>3200</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="N58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
+      <c r="O58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q58" s="3">
         <v>0</v>
@@ -2975,44 +3243,50 @@
       <c r="R58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3">
         <v>2500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>2500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="I59" s="3">
+        <v>5400</v>
+      </c>
+      <c r="J59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="K59" s="3">
+        <v>5000</v>
+      </c>
+      <c r="L59" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M59" s="3">
         <v>3600</v>
       </c>
-      <c r="G59" s="3">
-        <v>3600</v>
-      </c>
-      <c r="H59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="I59" s="3">
-        <v>5000</v>
-      </c>
-      <c r="J59" s="3">
-        <v>3800</v>
-      </c>
-      <c r="K59" s="3">
-        <v>3600</v>
-      </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>300</v>
       </c>
-      <c r="M59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3025,44 +3299,50 @@
       <c r="R59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F60" s="3">
         <v>5700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>5700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>3700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>300</v>
       </c>
-      <c r="M60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3075,16 +3355,22 @@
       <c r="R60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F61" s="3">
         <v>200</v>
@@ -3093,19 +3379,19 @@
         <v>200</v>
       </c>
       <c r="H61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3">
         <v>400</v>
       </c>
       <c r="K61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="M61" s="3">
         <v>0</v>
@@ -3125,8 +3411,14 @@
       <c r="R61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3">
+        <v>0</v>
+      </c>
+      <c r="T61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3143,19 +3435,19 @@
         <v>3</v>
       </c>
       <c r="H62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="I62" s="3">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="J62" s="3">
         <v>100</v>
       </c>
-      <c r="K62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>3</v>
+      <c r="K62" s="3">
+        <v>100</v>
+      </c>
+      <c r="L62" s="3">
+        <v>100</v>
       </c>
       <c r="M62" s="3" t="s">
         <v>3</v>
@@ -3166,17 +3458,23 @@
       <c r="O62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P62" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>0</v>
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3">
+        <v>0</v>
+      </c>
+      <c r="T62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3225,8 +3523,14 @@
       <c r="R63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3275,8 +3579,14 @@
       <c r="R64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3325,44 +3635,50 @@
       <c r="R65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2200</v>
+      </c>
+      <c r="F66" s="3">
         <v>6100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>6100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>7100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>7100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>6800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>6800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>9200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>4100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>400</v>
       </c>
-      <c r="M66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3375,8 +3691,14 @@
       <c r="R66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3395,8 +3717,10 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3445,8 +3769,14 @@
       <c r="R68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3495,8 +3825,14 @@
       <c r="R69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3545,8 +3881,14 @@
       <c r="R70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3595,44 +3937,50 @@
       <c r="R71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-76900</v>
+      </c>
+      <c r="F72" s="3">
         <v>-33600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-33600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-17800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-17800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-15000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-15000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-8500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>600</v>
       </c>
-      <c r="M72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3645,8 +3993,14 @@
       <c r="R72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3695,8 +4049,14 @@
       <c r="R73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3745,8 +4105,14 @@
       <c r="R74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3795,44 +4161,50 @@
       <c r="R75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8400</v>
+      </c>
+      <c r="F76" s="3">
         <v>50000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>50000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>3500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>3500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>5900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>7800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>600</v>
       </c>
-      <c r="M76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O76" s="3" t="s">
         <v>3</v>
       </c>
@@ -3845,8 +4217,14 @@
       <c r="R76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3895,113 +4273,131 @@
       <c r="R77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45596</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45504</v>
+      </c>
+      <c r="F80" s="2">
         <v>45412</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45322</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45230</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45138</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45046</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44957</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44865</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44135</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43951</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43769</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43585</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Q80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="R80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="T80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-21700</v>
+      </c>
+      <c r="F81" s="3">
         <v>-7900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-7900</v>
       </c>
-      <c r="F81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="I81" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="J81" s="3">
         <v>-3300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-3300</v>
       </c>
-      <c r="J81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3">
         <v>3500</v>
       </c>
-      <c r="L81" s="3">
-        <v>0</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
+        <v>0</v>
+      </c>
+      <c r="O81" s="3">
         <v>400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>200</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="R81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4020,46 +4416,48 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F83" s="3">
         <v>100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>100</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H83" s="3">
+      <c r="H83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J83" s="3">
         <v>100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>100</v>
       </c>
-      <c r="J83" s="3">
-        <v>0</v>
-      </c>
-      <c r="K83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
+      <c r="O83" s="3">
+        <v>0</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
@@ -4070,8 +4468,14 @@
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4120,8 +4524,14 @@
       <c r="R84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4170,8 +4580,14 @@
       <c r="R85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4220,8 +4636,14 @@
       <c r="R86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4270,8 +4692,14 @@
       <c r="R87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4320,47 +4748,53 @@
       <c r="R88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-25400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-25400</v>
       </c>
-      <c r="F89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="J89" s="3">
         <v>-1400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1400</v>
       </c>
-      <c r="J89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3">
         <v>-100</v>
       </c>
-      <c r="N89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4370,8 +4804,14 @@
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4390,8 +4830,10 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4413,23 +4855,23 @@
       <c r="I91" s="3">
         <v>0</v>
       </c>
-      <c r="J91" s="3" t="s">
-        <v>3</v>
+      <c r="J91" s="3">
+        <v>0</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="L91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3">
+        <v>0</v>
       </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
@@ -4440,8 +4882,14 @@
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4490,8 +4938,14 @@
       <c r="R92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4540,46 +4994,52 @@
       <c r="R93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>300</v>
+      </c>
+      <c r="F94" s="3">
         <v>-400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-400</v>
       </c>
-      <c r="F94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H94" s="3">
+        <v>200</v>
+      </c>
+      <c r="I94" s="3">
+        <v>200</v>
+      </c>
+      <c r="J94" s="3">
         <v>400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>400</v>
       </c>
-      <c r="J94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
+      <c r="O94" s="3">
+        <v>0</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
@@ -4590,8 +5050,14 @@
       <c r="R94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4610,8 +5076,10 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4636,11 +5104,11 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
-      </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -4660,8 +5128,14 @@
       <c r="R96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4710,8 +5184,14 @@
       <c r="R97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4760,8 +5240,14 @@
       <c r="R98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4810,47 +5296,53 @@
       <c r="R99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>300</v>
+      </c>
+      <c r="E100" s="3">
+        <v>300</v>
+      </c>
+      <c r="F100" s="3">
         <v>25300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>25300</v>
       </c>
-      <c r="F100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="I100" s="3">
+        <v>1400</v>
+      </c>
+      <c r="J100" s="3">
         <v>200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>200</v>
       </c>
-      <c r="J100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3">
         <v>100</v>
       </c>
-      <c r="N100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P100" s="3" t="s">
         <v>3</v>
       </c>
@@ -4860,46 +5352,52 @@
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H101" s="3">
+        <v>-100</v>
+      </c>
+      <c r="F101" s="3">
+        <v>0</v>
+      </c>
+      <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J101" s="3">
         <v>-200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-200</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -4910,47 +5408,53 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>300</v>
+      </c>
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
-        <v>0</v>
-      </c>
-      <c r="G102" s="3">
-        <v>0</v>
-      </c>
       <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
         <v>-800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-800</v>
       </c>
-      <c r="J102" s="3">
-        <v>0</v>
-      </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M102" s="3">
+      <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3">
         <v>-100</v>
       </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P102" s="3" t="s">
         <v>3</v>
       </c>
@@ -4958,6 +5462,12 @@
         <v>3</v>
       </c>
       <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/JZXN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="92">
   <si>
     <t>JZXN</t>
   </si>
@@ -656,261 +656,286 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="17" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="22" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45688</v>
+      </c>
+      <c r="F7" s="2">
         <v>45596</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45504</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45412</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45322</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45230</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45138</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45046</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44957</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44865</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44135</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43951</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43769</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43585</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S7" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="D8" s="3">
+        <v>500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>500</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H8" s="3">
         <v>1100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1100</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3">
+      <c r="J8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
         <v>300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>300</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O8" s="3">
         <v>8200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>500</v>
+      </c>
+      <c r="F9" s="3">
         <v>-1800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>-1800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>-600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>-600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>600</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3">
         <v>2200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>200</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+      <c r="F10" s="3">
         <v>1300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>-1300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>-1300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>-300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>-300</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3">
         <v>6000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -931,8 +956,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -987,8 +1014,14 @@
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1043,8 +1076,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1075,11 +1114,11 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
@@ -1099,8 +1138,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1123,19 +1168,19 @@
         <v>0</v>
       </c>
       <c r="J15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15" s="3">
         <v>100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="N15" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O15" s="3">
         <v>0</v>
@@ -1155,8 +1200,14 @@
       <c r="T15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="3">
+        <v>0</v>
+      </c>
+      <c r="V15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1174,120 +1225,134 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>800</v>
+      </c>
+      <c r="E17" s="3">
+        <v>800</v>
+      </c>
+      <c r="F17" s="3">
         <v>19500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>19500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>9100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>9100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>-1100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>-1100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>3400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3400</v>
       </c>
-      <c r="L17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3">
         <v>3800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>300</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S17" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E18" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F18" s="3">
         <v>-19900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>-19900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>-7900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>-7900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>-3100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>-3100</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3">
         <v>4400</v>
       </c>
-      <c r="N18" s="3">
-        <v>0</v>
-      </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="3">
         <v>500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>300</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1308,8 +1373,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1337,14 +1404,14 @@
       <c r="K20" s="3">
         <v>0</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>3</v>
+      <c r="L20" s="3">
+        <v>0</v>
       </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
+      <c r="N20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O20" s="3">
         <v>0</v>
@@ -1352,11 +1419,11 @@
       <c r="P20" s="3">
         <v>0</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
+      <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
+        <v>0</v>
       </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
@@ -1364,64 +1431,76 @@
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F21" s="3">
         <v>-19900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>-19900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>-7900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>-7900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>-3000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>-3000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>100</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3">
         <v>500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>300</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1444,17 +1523,17 @@
         <v>0</v>
       </c>
       <c r="J22" s="3">
+        <v>0</v>
+      </c>
+      <c r="K22" s="3">
+        <v>0</v>
+      </c>
+      <c r="L22" s="3">
         <v>100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>100</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1464,11 +1543,11 @@
       <c r="P22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S22" s="3">
         <v>0</v>
@@ -1476,64 +1555,76 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E23" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F23" s="3">
         <v>-19900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>-19900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>-7900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>-7900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>-3200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>-3200</v>
       </c>
-      <c r="L23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3">
         <v>4400</v>
       </c>
-      <c r="N23" s="3">
-        <v>0</v>
-      </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="3">
         <v>500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>300</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S23" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1549,11 +1640,11 @@
       <c r="G24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
+      <c r="H24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J24" s="3">
         <v>0</v>
@@ -1561,35 +1652,41 @@
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1644,120 +1741,138 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E26" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F26" s="3">
         <v>-19900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>-19900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>-7900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>-7900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>-3200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>-3200</v>
       </c>
-      <c r="L26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3">
         <v>3400</v>
       </c>
-      <c r="N26" s="3">
-        <v>0</v>
-      </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="3">
         <v>400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>200</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S26" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E27" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F27" s="3">
         <v>-21700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>-21700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>-7900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>-7900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>-1400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>-1400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>-3300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>-3300</v>
       </c>
-      <c r="L27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3">
         <v>3500</v>
       </c>
-      <c r="N27" s="3">
-        <v>0</v>
-      </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="3">
         <v>400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>200</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S27" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1812,46 +1927,52 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
         <v>-1700</v>
       </c>
-      <c r="E29" s="3">
+      <c r="G29" s="3">
         <v>-1700</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>-2200</v>
       </c>
-      <c r="I29" s="3">
+      <c r="K29" s="3">
         <v>-2200</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-100</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -1868,8 +1989,14 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1924,8 +2051,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1980,8 +2113,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2009,14 +2148,14 @@
       <c r="K32" s="3">
         <v>0</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>3</v>
+      <c r="L32" s="3">
+        <v>0</v>
       </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
+      <c r="N32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O32" s="3">
         <v>0</v>
@@ -2024,11 +2163,11 @@
       <c r="P32" s="3">
         <v>0</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
+      <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
+        <v>0</v>
       </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
@@ -2036,64 +2175,76 @@
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E33" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F33" s="3">
         <v>-21700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>-21700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>-7900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>-7900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>-1400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>-1400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>-3300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>-3300</v>
       </c>
-      <c r="L33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3">
         <v>3500</v>
       </c>
-      <c r="N33" s="3">
-        <v>0</v>
-      </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="3">
         <v>400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>200</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S33" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2148,125 +2299,143 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E35" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F35" s="3">
         <v>-21700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>-21700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>-7900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>-7900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>-1400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>-1400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>-3300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>-3300</v>
       </c>
-      <c r="L35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3">
         <v>3500</v>
       </c>
-      <c r="N35" s="3">
-        <v>0</v>
-      </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="3">
         <v>400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>200</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S35" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45688</v>
+      </c>
+      <c r="F38" s="2">
         <v>45596</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45504</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45412</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45322</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45230</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45138</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45046</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44957</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44865</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44135</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43951</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43769</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43585</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S38" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2287,8 +2456,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2309,49 +2480,51 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>300</v>
+      </c>
+      <c r="F41" s="3">
         <v>900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>800</v>
-      </c>
-      <c r="K41" s="3">
-        <v>800</v>
-      </c>
-      <c r="L41" s="3">
-        <v>2300</v>
       </c>
       <c r="M41" s="3">
         <v>800</v>
       </c>
       <c r="N41" s="3">
-        <v>0</v>
-      </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
+        <v>2300</v>
+      </c>
+      <c r="O41" s="3">
+        <v>800</v>
+      </c>
+      <c r="P41" s="3">
+        <v>0</v>
       </c>
       <c r="Q41" s="3" t="s">
         <v>3</v>
@@ -2365,8 +2538,14 @@
       <c r="T41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2395,14 +2574,14 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>600</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O42" s="3" t="s">
         <v>3</v>
       </c>
@@ -2412,17 +2591,23 @@
       <c r="Q42" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
-      <c r="S42" s="3">
-        <v>0</v>
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2433,38 +2618,38 @@
         <v>3</v>
       </c>
       <c r="F43" s="3">
+        <v>800</v>
+      </c>
+      <c r="G43" s="3">
+        <v>800</v>
+      </c>
+      <c r="H43" s="3">
         <v>3200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>3200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>1700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>5400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>5400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>6900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>5000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>600</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q43" s="3" t="s">
         <v>3</v>
       </c>
@@ -2477,8 +2662,14 @@
       <c r="T43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2488,38 +2679,38 @@
       <c r="E44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F44" s="3">
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3">
         <v>200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>200</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J44" s="3">
+      <c r="J44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
         <v>500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>200</v>
       </c>
-      <c r="N44" s="3">
-        <v>0</v>
-      </c>
-      <c r="O44" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
+      <c r="P44" s="3">
+        <v>0</v>
       </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
@@ -2533,50 +2724,56 @@
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>200</v>
+      </c>
+      <c r="F45" s="3">
         <v>100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>8100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>8100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>100</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2589,50 +2786,56 @@
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E46" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F46" s="3">
         <v>10600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>10600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>55500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>55500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>10500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>10500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>8700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>8700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>12200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>6500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>700</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q46" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,8 +2848,14 @@
       <c r="T46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2677,18 +2886,18 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O47" s="3">
         <v>5300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>300</v>
       </c>
-      <c r="O47" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2701,49 +2910,55 @@
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F48" s="3">
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H48" s="3">
         <v>700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>700</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
         <v>1200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>100</v>
       </c>
-      <c r="N48" s="3">
-        <v>0</v>
-      </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
+      <c r="P48" s="3">
+        <v>0</v>
       </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
@@ -2757,8 +2972,14 @@
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2795,11 +3016,11 @@
       <c r="N49" s="3">
         <v>0</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -2813,8 +3034,14 @@
       <c r="T49" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2869,8 +3096,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2925,8 +3158,14 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -2936,38 +3175,38 @@
       <c r="E52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F52" s="3">
+      <c r="F52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H52" s="3">
         <v>100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>900</v>
       </c>
-      <c r="J52" s="3">
-        <v>0</v>
-      </c>
-      <c r="K52" s="3">
-        <v>0</v>
-      </c>
       <c r="L52" s="3">
+        <v>0</v>
+      </c>
+      <c r="M52" s="3">
+        <v>0</v>
+      </c>
+      <c r="N52" s="3">
         <v>100</v>
       </c>
-      <c r="M52" s="3">
-        <v>0</v>
-      </c>
-      <c r="N52" s="3">
-        <v>0</v>
-      </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
+      <c r="O52" s="3">
+        <v>0</v>
+      </c>
+      <c r="P52" s="3">
+        <v>0</v>
       </c>
       <c r="Q52" s="3" t="s">
         <v>3</v>
@@ -2981,8 +3220,14 @@
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3037,50 +3282,56 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E54" s="3">
+        <v>9900</v>
+      </c>
+      <c r="F54" s="3">
         <v>10600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>10600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>56200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>56200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>11400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>11400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>10400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>10400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>15300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>11900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>1000</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3093,8 +3344,14 @@
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3115,8 +3372,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3137,49 +3396,51 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>700</v>
+      </c>
+      <c r="F57" s="3">
         <v>200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>200</v>
       </c>
-      <c r="F57" s="3">
-        <v>0</v>
-      </c>
-      <c r="G57" s="3">
-        <v>0</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J57" s="3">
-        <v>0</v>
-      </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>3</v>
+      <c r="H57" s="3">
+        <v>0</v>
+      </c>
+      <c r="I57" s="3">
+        <v>0</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
       </c>
       <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O57" s="3">
         <v>100</v>
       </c>
-      <c r="N57" s="3">
-        <v>0</v>
-      </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
+      <c r="P57" s="3">
+        <v>0</v>
       </c>
       <c r="Q57" s="3" t="s">
         <v>3</v>
@@ -3193,16 +3454,22 @@
       <c r="T57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>200</v>
@@ -3211,37 +3478,37 @@
         <v>200</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>3200</v>
       </c>
-      <c r="M58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O58" s="3" t="s">
         <v>3</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3249,50 +3516,56 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D59" s="3">
-        <v>0</v>
-      </c>
-      <c r="E59" s="3">
-        <v>0</v>
+      <c r="D59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F59" s="3">
+        <v>0</v>
+      </c>
+      <c r="G59" s="3">
+        <v>0</v>
+      </c>
+      <c r="H59" s="3">
         <v>2500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>2500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>5400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>5400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>5000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>300</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q59" s="3" t="s">
         <v>3</v>
       </c>
@@ -3305,50 +3578,56 @@
       <c r="T59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F60" s="3">
         <v>2200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>2200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>5700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>5700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>6700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>6700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>8300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>3700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>300</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q60" s="3" t="s">
         <v>3</v>
       </c>
@@ -3361,8 +3640,14 @@
       <c r="T60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3373,31 +3658,31 @@
         <v>0</v>
       </c>
       <c r="F61" s="3">
+        <v>0</v>
+      </c>
+      <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>200</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="L61" s="3">
         <v>400</v>
       </c>
       <c r="M61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="N61" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="O61" s="3">
         <v>0</v>
@@ -3417,8 +3702,14 @@
       <c r="T61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U61" s="3">
+        <v>0</v>
+      </c>
+      <c r="V61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -3434,26 +3725,26 @@
       <c r="G62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J62" s="3">
         <v>400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>400</v>
-      </c>
-      <c r="J62" s="3">
-        <v>100</v>
-      </c>
-      <c r="K62" s="3">
-        <v>100</v>
       </c>
       <c r="L62" s="3">
         <v>100</v>
       </c>
-      <c r="M62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N62" s="3" t="s">
-        <v>3</v>
+      <c r="M62" s="3">
+        <v>100</v>
+      </c>
+      <c r="N62" s="3">
+        <v>100</v>
       </c>
       <c r="O62" s="3" t="s">
         <v>3</v>
@@ -3464,17 +3755,23 @@
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R62" s="3">
-        <v>0</v>
-      </c>
-      <c r="S62" s="3">
-        <v>0</v>
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U62" s="3">
+        <v>0</v>
+      </c>
+      <c r="V62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3529,8 +3826,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3585,8 +3888,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3641,50 +3950,56 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E66" s="3">
+        <v>2400</v>
+      </c>
+      <c r="F66" s="3">
         <v>2200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>2200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>7100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>7100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>6800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>6800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>9200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>4100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>400</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q66" s="3" t="s">
         <v>3</v>
       </c>
@@ -3697,8 +4012,14 @@
       <c r="T66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3719,8 +4040,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3775,8 +4098,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3831,8 +4160,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3887,8 +4222,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3943,50 +4284,56 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="E72" s="3">
+        <v>-77600</v>
+      </c>
+      <c r="F72" s="3">
         <v>-76900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>-76900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>-33600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>-33600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>-17800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>-17800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>-15000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>-15000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>-8500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>600</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q72" s="3" t="s">
         <v>3</v>
       </c>
@@ -3999,8 +4346,14 @@
       <c r="T72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4055,8 +4408,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4111,8 +4470,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4167,50 +4532,56 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E76" s="3">
+        <v>7600</v>
+      </c>
+      <c r="F76" s="3">
         <v>8400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>50000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>50000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>4200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>4200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>3500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>3500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>7800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>600</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q76" s="3" t="s">
         <v>3</v>
       </c>
@@ -4223,8 +4594,14 @@
       <c r="T76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4279,125 +4656,143 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45777</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45688</v>
+      </c>
+      <c r="F80" s="2">
         <v>45596</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45504</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45412</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45322</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45230</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45138</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45046</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44957</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44865</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44135</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43951</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43769</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43585</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="S80" s="2" t="s">
         <v>3</v>
       </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="V80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E81" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F81" s="3">
         <v>-21700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>-21700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>-7900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>-7900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>-1400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>-1400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>-3300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>-3300</v>
       </c>
-      <c r="L81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3">
         <v>3500</v>
       </c>
-      <c r="N81" s="3">
-        <v>0</v>
-      </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="3">
         <v>400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>200</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S81" s="3" t="s">
         <v>3</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4418,52 +4813,54 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>100</v>
+      </c>
+      <c r="F83" s="3">
         <v>-100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>-100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>100</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
         <v>100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>100</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
+      <c r="Q83" s="3">
+        <v>0</v>
       </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
@@ -4474,8 +4871,14 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4530,8 +4933,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4586,8 +4995,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4642,8 +5057,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4698,8 +5119,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4754,53 +5181,59 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-400</v>
+      </c>
+      <c r="F89" s="3">
         <v>100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-25400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-25400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-1600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-1600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O89" s="3">
+      <c r="O89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3">
         <v>-100</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R89" s="3" t="s">
         <v>3</v>
       </c>
@@ -4810,8 +5243,14 @@
       <c r="T89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4832,16 +5271,18 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3">
+        <v>0</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>3</v>
@@ -4849,11 +5290,11 @@
       <c r="G91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
+      <c r="H91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J91" s="3">
         <v>0</v>
@@ -4861,23 +5302,23 @@
       <c r="K91" s="3">
         <v>0</v>
       </c>
-      <c r="L91" s="3" t="s">
-        <v>3</v>
+      <c r="L91" s="3">
+        <v>0</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
       </c>
-      <c r="N91" s="3">
-        <v>0</v>
+      <c r="N91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O91" s="3">
         <v>0</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="3">
+        <v>0</v>
       </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
@@ -4888,8 +5329,14 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4944,8 +5391,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5000,52 +5453,58 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>0</v>
+      </c>
+      <c r="E94" s="3">
+        <v>0</v>
+      </c>
+      <c r="F94" s="3">
         <v>300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>400</v>
       </c>
-      <c r="L94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O94" s="3">
-        <v>0</v>
+      <c r="O94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5056,8 +5515,14 @@
       <c r="T94" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5078,8 +5543,10 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5110,11 +5577,11 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
-      <c r="N96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O96" s="3">
         <v>0</v>
@@ -5134,8 +5601,14 @@
       <c r="T96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5190,8 +5663,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5246,8 +5725,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5302,53 +5787,59 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3">
+        <v>0</v>
+      </c>
+      <c r="F100" s="3">
         <v>300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>25300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>25300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>1400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>1400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>200</v>
       </c>
-      <c r="L100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O100" s="3">
+      <c r="O100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3">
         <v>100</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R100" s="3" t="s">
         <v>3</v>
       </c>
@@ -5358,52 +5849,58 @@
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J101" s="3">
+      <c r="H101" s="3">
+        <v>0</v>
+      </c>
+      <c r="I101" s="3">
+        <v>0</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -5414,53 +5911,59 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V101" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-300</v>
+      </c>
+      <c r="F102" s="3">
         <v>300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
+        <v>0</v>
+      </c>
+      <c r="K102" s="3">
+        <v>0</v>
+      </c>
+      <c r="L102" s="3">
         <v>-800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-800</v>
       </c>
-      <c r="L102" s="3">
-        <v>0</v>
-      </c>
-      <c r="M102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O102" s="3">
+      <c r="N102" s="3">
+        <v>0</v>
+      </c>
+      <c r="O102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3">
         <v>-100</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R102" s="3" t="s">
         <v>3</v>
       </c>
@@ -5468,6 +5971,12 @@
         <v>3</v>
       </c>
       <c r="T102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
